--- a/data/raw/TALENT ACQUISITION [Khusus Progress Recruit]KCM.xlsx
+++ b/data/raw/TALENT ACQUISITION [Khusus Progress Recruit]KCM.xlsx
@@ -428,7 +428,7 @@
         <v>TALENT ACQUISITION [Khusus Progress Recruit]KCM</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-06-09</v>
       </c>
     </row>
   </sheetData>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S314"/>
+  <dimension ref="A1:S326"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -542,10 +542,10 @@
         <v>Medium</v>
       </c>
       <c r="G2" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>2024-08-01</v>
@@ -566,7 +566,7 @@
         <v>2025-01-28</v>
       </c>
       <c r="O2" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -604,7 +604,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I3" t="str">
         <v>2024-08-01</v>
@@ -661,7 +661,7 @@
         <v>Important</v>
       </c>
       <c r="G4" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v>2024-08-02</v>
@@ -890,7 +890,7 @@
         <v>Host Hunting</v>
       </c>
       <c r="C8" t="str">
-        <v>In Progress (Untuk Task selain Recruitment Reguler)</v>
+        <v>Untuk Task selain Recruitment Reguler</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -902,10 +902,10 @@
         <v>Important</v>
       </c>
       <c r="G8" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H8" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I8" t="str">
         <v>2024-08-02</v>
@@ -926,7 +926,7 @@
         <v>2025-05-12</v>
       </c>
       <c r="O8" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -958,10 +958,10 @@
         <v>Important</v>
       </c>
       <c r="G9" t="str">
-        <v>;;;Adelia Galuh H</v>
+        <v>;;;</v>
       </c>
       <c r="H9" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I9" t="str">
         <v>2024-08-06</v>
@@ -1017,7 +1017,7 @@
         <v>Important</v>
       </c>
       <c r="G10" t="str">
-        <v>;Novinda Riski</v>
+        <v>;</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -1076,10 +1076,10 @@
         <v>Low</v>
       </c>
       <c r="G11" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I11" t="str">
         <v>2024-08-14</v>
@@ -1138,10 +1138,10 @@
         <v>Important</v>
       </c>
       <c r="G12" t="str">
-        <v>;;Adelia Galuh H</v>
+        <v>;;</v>
       </c>
       <c r="H12" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I12" t="str">
         <v>2024-08-15</v>
@@ -1162,7 +1162,7 @@
         <v>2024-09-11</v>
       </c>
       <c r="O12" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P12" t="str">
         <v>2/2</v>
@@ -1260,7 +1260,7 @@
         <v>;</v>
       </c>
       <c r="H14" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I14" t="str">
         <v>2024-08-21</v>
@@ -1396,7 +1396,7 @@
         <v>2024-11-07</v>
       </c>
       <c r="O16" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P16" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v>2025-03-04</v>
       </c>
       <c r="O18" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P18" t="str">
         <v>3/4</v>
@@ -1608,7 +1608,7 @@
         <v>;;</v>
       </c>
       <c r="H20" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I20" t="str">
         <v>2024-08-30</v>
@@ -1629,7 +1629,7 @@
         <v>2024-10-01</v>
       </c>
       <c r="O20" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P20" t="str">
         <v/>
@@ -1720,10 +1720,10 @@
         <v>Low</v>
       </c>
       <c r="G22" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H22" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I22" t="str">
         <v>2024-09-12</v>
@@ -1780,10 +1780,10 @@
         <v>Medium</v>
       </c>
       <c r="G23" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I23" t="str">
         <v>2024-09-13</v>
@@ -1839,10 +1839,10 @@
         <v>Medium</v>
       </c>
       <c r="G24" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I24" t="str">
         <v>2024-09-23</v>
@@ -1863,7 +1863,7 @@
         <v>2025-01-28</v>
       </c>
       <c r="O24" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P24" t="str">
         <v/>
@@ -1922,7 +1922,7 @@
         <v>2025-04-06</v>
       </c>
       <c r="O25" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P25" t="str">
         <v/>
@@ -1978,7 +1978,7 @@
         <v>2025-01-28</v>
       </c>
       <c r="O26" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P26" t="str">
         <v/>
@@ -2010,10 +2010,10 @@
         <v>Urgent</v>
       </c>
       <c r="G27" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I27" t="str">
         <v>2024-10-28</v>
@@ -2034,7 +2034,7 @@
         <v>2025-01-28</v>
       </c>
       <c r="O27" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P27" t="str">
         <v/>
@@ -2070,10 +2070,10 @@
         <v>Important</v>
       </c>
       <c r="G28" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I28" t="str">
         <v>2024-10-28</v>
@@ -2094,7 +2094,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O28" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P28" t="str">
         <v/>
@@ -2132,7 +2132,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I29" t="str">
         <v>2024-10-31</v>
@@ -2153,7 +2153,7 @@
         <v>2025-02-14</v>
       </c>
       <c r="O29" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P29" t="str">
         <v/>
@@ -2365,7 +2365,7 @@
         <v>Medium</v>
       </c>
       <c r="G33" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -2389,7 +2389,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O33" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P33" t="str">
         <v>1/1</v>
@@ -2426,10 +2426,10 @@
         <v>Medium</v>
       </c>
       <c r="G34" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H34" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I34" t="str">
         <v>2024-11-20</v>
@@ -2496,10 +2496,10 @@
         <v>Important</v>
       </c>
       <c r="G35" t="str">
-        <v>;Novinda Riski</v>
+        <v>;</v>
       </c>
       <c r="H35" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I35" t="str">
         <v>2024-11-21</v>
@@ -2520,7 +2520,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O35" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P35" t="str">
         <v/>
@@ -2555,10 +2555,10 @@
         <v>Important</v>
       </c>
       <c r="G36" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="H36" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I36" t="str">
         <v>2024-11-21</v>
@@ -2579,7 +2579,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O36" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P36" t="str">
         <v/>
@@ -2614,10 +2614,10 @@
         <v>Medium</v>
       </c>
       <c r="G37" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H37" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I37" t="str">
         <v>2024-11-22</v>
@@ -2638,7 +2638,7 @@
         <v>2025-03-25</v>
       </c>
       <c r="O37" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P37" t="str">
         <v/>
@@ -2675,10 +2675,10 @@
         <v>Medium</v>
       </c>
       <c r="G38" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H38" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I38" t="str">
         <v>2024-12-02</v>
@@ -2699,7 +2699,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O38" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P38" t="str">
         <v>1/1</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I39" t="str">
         <v>2024-12-05</v>
@@ -2804,10 +2804,10 @@
         <v>Medium</v>
       </c>
       <c r="G40" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H40" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I40" t="str">
         <v>2024-12-05</v>
@@ -2828,7 +2828,7 @@
         <v>2025-03-25</v>
       </c>
       <c r="O40" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P40" t="str">
         <v>2/2</v>
@@ -2866,10 +2866,10 @@
         <v>Important</v>
       </c>
       <c r="G41" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H41" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I41" t="str">
         <v>2024-12-05</v>
@@ -2890,7 +2890,7 @@
         <v>2025-01-28</v>
       </c>
       <c r="O41" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P41" t="str">
         <v/>
@@ -2927,10 +2927,10 @@
         <v>Medium</v>
       </c>
       <c r="G42" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I42" t="str">
         <v>2024-12-05</v>
@@ -2951,7 +2951,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O42" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P42" t="str">
         <v>2/2</v>
@@ -3054,7 +3054,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I44" t="str">
         <v>2024-12-10</v>
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I45" t="str">
         <v>2024-12-10</v>
@@ -3137,7 +3137,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O45" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P45" t="str">
         <v>0/1</v>
@@ -3175,7 +3175,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I46" t="str">
         <v>2024-12-17</v>
@@ -3196,7 +3196,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O46" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P46" t="str">
         <v/>
@@ -3232,10 +3232,10 @@
         <v>Medium</v>
       </c>
       <c r="G47" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H47" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I47" t="str">
         <v>2024-12-17</v>
@@ -3256,7 +3256,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O47" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P47" t="str">
         <v/>
@@ -3294,10 +3294,10 @@
         <v>Medium</v>
       </c>
       <c r="G48" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H48" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I48" t="str">
         <v>2024-12-17</v>
@@ -3318,7 +3318,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O48" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P48" t="str">
         <v>0/1</v>
@@ -3357,7 +3357,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I49" t="str">
         <v>2024-12-18</v>
@@ -3378,7 +3378,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O49" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P49" t="str">
         <v>0/1</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I50" t="str">
         <v>2024-12-18</v>
@@ -3477,10 +3477,10 @@
         <v>Medium</v>
       </c>
       <c r="G51" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H51" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I51" t="str">
         <v>2024-12-20</v>
@@ -3501,7 +3501,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O51" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P51" t="str">
         <v/>
@@ -3538,10 +3538,10 @@
         <v>Medium</v>
       </c>
       <c r="G52" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H52" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I52" t="str">
         <v>2024-12-23</v>
@@ -3562,7 +3562,7 @@
         <v>2025-04-11</v>
       </c>
       <c r="O52" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P52" t="str">
         <v>0/1</v>
@@ -3602,7 +3602,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I53" t="str">
         <v>2025-01-03</v>
@@ -3685,7 +3685,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O54" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P54" t="str">
         <v>0/1</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I55" t="str">
         <v>2025-01-07</v>
@@ -3746,7 +3746,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O55" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P55" t="str">
         <v>0/1</v>
@@ -3782,10 +3782,10 @@
         <v>Low</v>
       </c>
       <c r="G56" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H56" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I56" t="str">
         <v>2025-01-07</v>
@@ -3843,10 +3843,10 @@
         <v>Medium</v>
       </c>
       <c r="G57" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H57" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v>2025-01-13</v>
@@ -3867,7 +3867,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O57" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P57" t="str">
         <v/>
@@ -4041,7 +4041,7 @@
         <v>2025-03-13</v>
       </c>
       <c r="O60" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P60" t="str">
         <v>2/2</v>
@@ -4073,10 +4073,10 @@
         <v>Important</v>
       </c>
       <c r="G61" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H61" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I61" t="str">
         <v>2025-01-20</v>
@@ -4097,7 +4097,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O61" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P61" t="str">
         <v>3/4</v>
@@ -4217,7 +4217,7 @@
         <v>2026-01-09</v>
       </c>
       <c r="O63" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P63" t="str">
         <v>1/1</v>
@@ -4254,10 +4254,10 @@
         <v>Important</v>
       </c>
       <c r="G64" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H64" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I64" t="str">
         <v>2025-01-20</v>
@@ -4278,7 +4278,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O64" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P64" t="str">
         <v/>
@@ -4313,10 +4313,10 @@
         <v>Important</v>
       </c>
       <c r="G65" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H65" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I65" t="str">
         <v>2025-01-20</v>
@@ -4337,7 +4337,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O65" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P65" t="str">
         <v>2/3</v>
@@ -4379,7 +4379,7 @@
         <v>;</v>
       </c>
       <c r="H66" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I66" t="str">
         <v>2025-01-20</v>
@@ -4440,7 +4440,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I67" t="str">
         <v>2025-01-20</v>
@@ -4461,7 +4461,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O67" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P67" t="str">
         <v>0/1</v>
@@ -4581,7 +4581,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O69" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P69" t="str">
         <v>0/2</v>
@@ -4681,7 +4681,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I71" t="str">
         <v>2025-01-24</v>
@@ -4702,7 +4702,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O71" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P71" t="str">
         <v>0/1</v>
@@ -4741,7 +4741,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I72" t="str">
         <v>2025-01-24</v>
@@ -4800,7 +4800,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I73" t="str">
         <v>2025-01-24</v>
@@ -4859,7 +4859,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I74" t="str">
         <v>2025-01-24</v>
@@ -4880,7 +4880,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O74" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P74" t="str">
         <v>0/1</v>
@@ -4915,10 +4915,10 @@
         <v>Important</v>
       </c>
       <c r="G75" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H75" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I75" t="str">
         <v>2025-01-24</v>
@@ -4939,7 +4939,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O75" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P75" t="str">
         <v>1/2</v>
@@ -4978,10 +4978,10 @@
         <v>Low</v>
       </c>
       <c r="G76" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H76" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I76" t="str">
         <v>2025-01-24</v>
@@ -5037,10 +5037,10 @@
         <v>Low</v>
       </c>
       <c r="G77" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H77" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I77" t="str">
         <v>2025-01-24</v>
@@ -5099,7 +5099,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I78" t="str">
         <v>2025-01-24</v>
@@ -5120,7 +5120,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O78" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P78" t="str">
         <v/>
@@ -5158,7 +5158,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I79" t="str">
         <v>2025-01-24</v>
@@ -5179,7 +5179,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O79" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P79" t="str">
         <v>1/1</v>
@@ -5218,7 +5218,7 @@
         <v>;</v>
       </c>
       <c r="H80" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I80" t="str">
         <v>2025-01-24</v>
@@ -5277,7 +5277,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I81" t="str">
         <v>2025-01-24</v>
@@ -5298,7 +5298,7 @@
         <v>2025-04-28</v>
       </c>
       <c r="O81" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P81" t="str">
         <v>1/1</v>
@@ -5337,10 +5337,10 @@
         <v>Medium</v>
       </c>
       <c r="G82" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H82" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I82" t="str">
         <v>2025-01-24</v>
@@ -5401,10 +5401,10 @@
         <v>Medium</v>
       </c>
       <c r="G83" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H83" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I83" t="str">
         <v>2025-01-28</v>
@@ -5425,7 +5425,7 @@
         <v>2025-08-04</v>
       </c>
       <c r="O83" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P83" t="str">
         <v>2/2</v>
@@ -5465,10 +5465,10 @@
         <v>Medium</v>
       </c>
       <c r="G84" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H84" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I84" t="str">
         <v>2025-01-28</v>
@@ -5489,7 +5489,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O84" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P84" t="str">
         <v>3/3</v>
@@ -5527,7 +5527,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I85" t="str">
         <v>2025-01-28</v>
@@ -5706,10 +5706,10 @@
         <v>Medium</v>
       </c>
       <c r="G88" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H88" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I88" t="str">
         <v>2025-01-31</v>
@@ -5730,7 +5730,7 @@
         <v>2025-03-25</v>
       </c>
       <c r="O88" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P88" t="str">
         <v>0/1</v>
@@ -5770,7 +5770,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I89" t="str">
         <v>2025-02-03</v>
@@ -5895,7 +5895,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I91" t="str">
         <v>2025-02-06</v>
@@ -5916,7 +5916,7 @@
         <v>2025-03-04</v>
       </c>
       <c r="O91" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P91" t="str">
         <v>1/2</v>
@@ -5976,7 +5976,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O92" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P92" t="str">
         <v>0/1</v>
@@ -6017,7 +6017,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I93" t="str">
         <v>2025-02-06</v>
@@ -6070,10 +6070,10 @@
         <v>Medium</v>
       </c>
       <c r="G94" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H94" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I94" t="str">
         <v>2025-02-06</v>
@@ -6094,7 +6094,7 @@
         <v>2025-03-25</v>
       </c>
       <c r="O94" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P94" t="str">
         <v>2/2</v>
@@ -6131,10 +6131,10 @@
         <v>Medium</v>
       </c>
       <c r="G95" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H95" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I95" t="str">
         <v>2025-02-06</v>
@@ -6155,7 +6155,7 @@
         <v>2025-03-25</v>
       </c>
       <c r="O95" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P95" t="str">
         <v>0/1</v>
@@ -6195,7 +6195,7 @@
         <v>;</v>
       </c>
       <c r="H96" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I96" t="str">
         <v>2025-02-07</v>
@@ -6279,7 +6279,7 @@
         <v>2025-03-04</v>
       </c>
       <c r="O97" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P97" t="str">
         <v>0/1</v>
@@ -6317,7 +6317,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I98" t="str">
         <v>2025-02-07</v>
@@ -6338,7 +6338,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O98" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P98" t="str">
         <v>0/1</v>
@@ -6370,10 +6370,10 @@
         <v>Medium</v>
       </c>
       <c r="G99" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H99" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I99" t="str">
         <v>2025-02-07</v>
@@ -6394,7 +6394,7 @@
         <v>2025-04-04</v>
       </c>
       <c r="O99" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P99" t="str">
         <v>3/3</v>
@@ -6554,7 +6554,7 @@
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I102" t="str">
         <v>2025-02-19</v>
@@ -6614,7 +6614,7 @@
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I103" t="str">
         <v>2025-02-19</v>
@@ -6844,7 +6844,7 @@
         <v>Medium</v>
       </c>
       <c r="G107" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H107" t="str">
         <v/>
@@ -6868,7 +6868,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O107" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P107" t="str">
         <v/>
@@ -6909,7 +6909,7 @@
         <v/>
       </c>
       <c r="H108" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I108" t="str">
         <v>2025-03-05</v>
@@ -6972,7 +6972,7 @@
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I109" t="str">
         <v>2025-03-18</v>
@@ -7108,7 +7108,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O111" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P111" t="str">
         <v/>
@@ -7262,10 +7262,10 @@
         <v>Medium</v>
       </c>
       <c r="G114" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I114" t="str">
         <v>2025-04-04</v>
@@ -7321,10 +7321,10 @@
         <v>Medium</v>
       </c>
       <c r="G115" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I115" t="str">
         <v>2025-04-04</v>
@@ -7616,10 +7616,10 @@
         <v>Medium</v>
       </c>
       <c r="G120" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H120" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I120" t="str">
         <v>2025-04-04</v>
@@ -7663,19 +7663,19 @@
         <v>Product Designer</v>
       </c>
       <c r="C121" t="str">
-        <v>Offering</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D121" t="str">
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F121" t="str">
         <v>Important</v>
       </c>
       <c r="G121" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H121" t="str">
         <v/>
@@ -7696,7 +7696,7 @@
         <v>false</v>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O121" t="str">
         <v/>
@@ -7759,7 +7759,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O122" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P122" t="str">
         <v/>
@@ -7916,10 +7916,10 @@
         <v>Medium</v>
       </c>
       <c r="G125" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H125" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I125" t="str">
         <v>2025-04-08</v>
@@ -7975,10 +7975,10 @@
         <v>Medium</v>
       </c>
       <c r="G126" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H126" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I126" t="str">
         <v>2025-04-08</v>
@@ -7999,7 +7999,7 @@
         <v>2025-05-13</v>
       </c>
       <c r="O126" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P126" t="str">
         <v>0/1</v>
@@ -8093,7 +8093,7 @@
         <v>Medium</v>
       </c>
       <c r="G128" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H128" t="str">
         <v/>
@@ -8117,7 +8117,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O128" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P128" t="str">
         <v/>
@@ -8280,10 +8280,10 @@
         <v>Medium</v>
       </c>
       <c r="G131" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H131" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I131" t="str">
         <v>2025-04-16</v>
@@ -8340,10 +8340,10 @@
         <v>Medium</v>
       </c>
       <c r="G132" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H132" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I132" t="str">
         <v>2025-04-16</v>
@@ -8424,7 +8424,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O133" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P133" t="str">
         <v/>
@@ -8644,7 +8644,7 @@
         <v>Medium</v>
       </c>
       <c r="G137" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H137" t="str">
         <v/>
@@ -8821,7 +8821,7 @@
         <v>Urgent</v>
       </c>
       <c r="G140" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H140" t="str">
         <v/>
@@ -8880,10 +8880,10 @@
         <v>Medium</v>
       </c>
       <c r="G141" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H141" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I141" t="str">
         <v>2025-05-13</v>
@@ -8904,7 +8904,7 @@
         <v>2025-11-24</v>
       </c>
       <c r="O141" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P141" t="str">
         <v/>
@@ -8939,10 +8939,10 @@
         <v>Medium</v>
       </c>
       <c r="G142" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H142" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I142" t="str">
         <v>2025-05-13</v>
@@ -8998,10 +8998,10 @@
         <v>Important</v>
       </c>
       <c r="G143" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H143" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I143" t="str">
         <v>2025-05-13</v>
@@ -9058,10 +9058,10 @@
         <v>Medium</v>
       </c>
       <c r="G144" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H144" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I144" t="str">
         <v>2025-05-13</v>
@@ -9176,7 +9176,7 @@
         <v>Medium</v>
       </c>
       <c r="G146" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H146" t="str">
         <v/>
@@ -9200,7 +9200,7 @@
         <v>2025-12-23</v>
       </c>
       <c r="O146" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P146" t="str">
         <v/>
@@ -9323,10 +9323,10 @@
         <v>Medium</v>
       </c>
       <c r="G148" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H148" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I148" t="str">
         <v>2025-05-19</v>
@@ -9382,10 +9382,10 @@
         <v>Medium</v>
       </c>
       <c r="G149" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H149" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I149" t="str">
         <v>2025-05-20</v>
@@ -9406,7 +9406,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O149" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P149" t="str">
         <v/>
@@ -9441,10 +9441,10 @@
         <v>Medium</v>
       </c>
       <c r="G150" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H150" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I150" t="str">
         <v>2025-05-20</v>
@@ -9501,10 +9501,10 @@
         <v>Medium</v>
       </c>
       <c r="G151" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H151" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I151" t="str">
         <v>2025-05-28</v>
@@ -9560,10 +9560,10 @@
         <v>Medium</v>
       </c>
       <c r="G152" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H152" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I152" t="str">
         <v>2025-05-28</v>
@@ -9677,10 +9677,10 @@
         <v>Urgent</v>
       </c>
       <c r="G154" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H154" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I154" t="str">
         <v>2025-06-03</v>
@@ -9701,7 +9701,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O154" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P154" t="str">
         <v/>
@@ -9733,10 +9733,10 @@
         <v>Urgent</v>
       </c>
       <c r="G155" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H155" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I155" t="str">
         <v>2025-06-03</v>
@@ -9757,7 +9757,7 @@
         <v>2025-10-13</v>
       </c>
       <c r="O155" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P155" t="str">
         <v/>
@@ -9789,10 +9789,10 @@
         <v>Urgent</v>
       </c>
       <c r="G156" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H156" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I156" t="str">
         <v>2025-06-03</v>
@@ -9813,7 +9813,7 @@
         <v>2025-09-08</v>
       </c>
       <c r="O156" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P156" t="str">
         <v/>
@@ -9845,10 +9845,10 @@
         <v>Medium</v>
       </c>
       <c r="G157" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H157" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I157" t="str">
         <v>2025-06-03</v>
@@ -9869,7 +9869,7 @@
         <v>2026-01-09</v>
       </c>
       <c r="O157" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P157" t="str">
         <v/>
@@ -9901,10 +9901,10 @@
         <v>Urgent</v>
       </c>
       <c r="G158" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H158" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I158" t="str">
         <v>2025-06-03</v>
@@ -9925,7 +9925,7 @@
         <v>2026-01-09</v>
       </c>
       <c r="O158" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P158" t="str">
         <v/>
@@ -9957,10 +9957,10 @@
         <v>Urgent</v>
       </c>
       <c r="G159" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H159" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I159" t="str">
         <v>2025-06-03</v>
@@ -9981,7 +9981,7 @@
         <v>2026-01-09</v>
       </c>
       <c r="O159" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P159" t="str">
         <v/>
@@ -10037,7 +10037,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O160" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P160" t="str">
         <v/>
@@ -10105,7 +10105,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O161" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P161" t="str">
         <v/>
@@ -10252,7 +10252,7 @@
         <v>Medium</v>
       </c>
       <c r="G164" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H164" t="str">
         <v/>
@@ -10276,7 +10276,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O164" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P164" t="str">
         <v/>
@@ -10308,7 +10308,7 @@
         <v>Medium</v>
       </c>
       <c r="G165" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H165" t="str">
         <v/>
@@ -10364,7 +10364,7 @@
         <v>Medium</v>
       </c>
       <c r="G166" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H166" t="str">
         <v/>
@@ -10388,7 +10388,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O166" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P166" t="str">
         <v/>
@@ -10420,7 +10420,7 @@
         <v>Medium</v>
       </c>
       <c r="G167" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H167" t="str">
         <v/>
@@ -10444,7 +10444,7 @@
         <v>2025-07-15</v>
       </c>
       <c r="O167" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P167" t="str">
         <v/>
@@ -10538,7 +10538,7 @@
         <v>Medium</v>
       </c>
       <c r="G169" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H169" t="str">
         <v/>
@@ -10597,7 +10597,7 @@
         <v>Medium</v>
       </c>
       <c r="G170" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H170" t="str">
         <v/>
@@ -10621,7 +10621,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O170" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P170" t="str">
         <v/>
@@ -10644,7 +10644,7 @@
         <v>Sr. Strategic Planner StratX (Grid)</v>
       </c>
       <c r="C171" t="str">
-        <v>Offering</v>
+        <v>Order for Contract Sign &amp; ID dkk</v>
       </c>
       <c r="D171" t="str">
         <v/>
@@ -10656,7 +10656,7 @@
         <v>Medium</v>
       </c>
       <c r="G171" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H171" t="str">
         <v/>
@@ -10859,7 +10859,7 @@
         <v>2025-08-01</v>
       </c>
       <c r="O174" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P174" t="str">
         <v/>
@@ -10952,7 +10952,7 @@
         <v>Medium</v>
       </c>
       <c r="G176" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H176" t="str">
         <v/>
@@ -11008,10 +11008,10 @@
         <v>Medium</v>
       </c>
       <c r="G177" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H177" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I177" t="str">
         <v>2025-07-10</v>
@@ -11032,7 +11032,7 @@
         <v>2025-09-08</v>
       </c>
       <c r="O177" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P177" t="str">
         <v/>
@@ -11147,7 +11147,7 @@
         <v>2025-09-08</v>
       </c>
       <c r="O179" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P179" t="str">
         <v/>
@@ -11179,7 +11179,7 @@
         <v>Medium</v>
       </c>
       <c r="G180" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H180" t="str">
         <v/>
@@ -11203,7 +11203,7 @@
         <v>2025-09-26</v>
       </c>
       <c r="O180" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P180" t="str">
         <v/>
@@ -11238,7 +11238,7 @@
         <v>;</v>
       </c>
       <c r="H181" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I181" t="str">
         <v>2025-07-25</v>
@@ -11302,10 +11302,10 @@
         <v>Medium</v>
       </c>
       <c r="G182" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H182" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I182" t="str">
         <v>2025-07-25</v>
@@ -11326,7 +11326,7 @@
         <v>2025-09-08</v>
       </c>
       <c r="O182" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P182" t="str">
         <v/>
@@ -11423,7 +11423,7 @@
         <v/>
       </c>
       <c r="H184" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I184" t="str">
         <v>2025-07-30</v>
@@ -11483,7 +11483,7 @@
         <v/>
       </c>
       <c r="H185" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I185" t="str">
         <v>2025-07-30</v>
@@ -11689,7 +11689,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O188" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P188" t="str">
         <v/>
@@ -11724,10 +11724,10 @@
         <v>Medium</v>
       </c>
       <c r="G189" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H189" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I189" t="str">
         <v>2025-08-05</v>
@@ -11785,10 +11785,10 @@
         <v>Medium</v>
       </c>
       <c r="G190" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H190" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I190" t="str">
         <v>2025-08-05</v>
@@ -11966,10 +11966,10 @@
         <v>Medium</v>
       </c>
       <c r="G193" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H193" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I193" t="str">
         <v>2025-08-06</v>
@@ -11990,7 +11990,7 @@
         <v>2025-12-16</v>
       </c>
       <c r="O193" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P193" t="str">
         <v/>
@@ -12045,10 +12045,10 @@
         <v>Medium</v>
       </c>
       <c r="G194" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H194" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I194" t="str">
         <v>2025-08-07</v>
@@ -12069,7 +12069,7 @@
         <v>2025-10-07</v>
       </c>
       <c r="O194" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P194" t="str">
         <v>3/3</v>
@@ -12107,7 +12107,7 @@
         <v/>
       </c>
       <c r="H195" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I195" t="str">
         <v>2025-08-11</v>
@@ -12167,7 +12167,7 @@
         <v/>
       </c>
       <c r="H196" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I196" t="str">
         <v>2025-08-11</v>
@@ -12188,7 +12188,7 @@
         <v>2025-11-10</v>
       </c>
       <c r="O196" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P196" t="str">
         <v/>
@@ -12317,7 +12317,7 @@
         <v>2025-10-06</v>
       </c>
       <c r="O198" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P198" t="str">
         <v/>
@@ -12422,10 +12422,10 @@
         <v>Medium</v>
       </c>
       <c r="G200" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H200" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I200" t="str">
         <v>2025-08-22</v>
@@ -12446,7 +12446,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O200" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P200" t="str">
         <v/>
@@ -12484,7 +12484,7 @@
         <v/>
       </c>
       <c r="H201" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I201" t="str">
         <v>2025-08-22</v>
@@ -12548,7 +12548,7 @@
         <v/>
       </c>
       <c r="H202" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I202" t="str">
         <v>2025-08-22</v>
@@ -12607,7 +12607,7 @@
         <v/>
       </c>
       <c r="H203" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I203" t="str">
         <v>2025-08-22</v>
@@ -12628,7 +12628,7 @@
         <v>2025-09-26</v>
       </c>
       <c r="O203" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P203" t="str">
         <v/>
@@ -12675,7 +12675,7 @@
         <v/>
       </c>
       <c r="H204" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I204" t="str">
         <v>2025-08-22</v>
@@ -12719,22 +12719,22 @@
         <v>Product Designer = Video Content Creator AI</v>
       </c>
       <c r="C205" t="str">
-        <v>Offering</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D205" t="str">
         <v/>
       </c>
       <c r="E205" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F205" t="str">
         <v>Medium</v>
       </c>
       <c r="G205" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H205" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I205" t="str">
         <v>2025-08-27</v>
@@ -12752,10 +12752,10 @@
         <v>false</v>
       </c>
       <c r="N205" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="O205" t="str">
-        <v/>
+        <v>Netri Alia Rahmi</v>
       </c>
       <c r="P205" t="str">
         <v/>
@@ -12790,10 +12790,10 @@
         <v>Medium</v>
       </c>
       <c r="G206" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H206" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I206" t="str">
         <v>2025-08-27</v>
@@ -12814,7 +12814,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O206" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P206" t="str">
         <v/>
@@ -12852,7 +12852,7 @@
         <v/>
       </c>
       <c r="H207" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I207" t="str">
         <v>2025-08-27</v>
@@ -12908,10 +12908,10 @@
         <v>Medium</v>
       </c>
       <c r="G208" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H208" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I208" t="str">
         <v>2025-08-28</v>
@@ -12932,7 +12932,7 @@
         <v>2025-10-13</v>
       </c>
       <c r="O208" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P208" t="str">
         <v>0/3</v>
@@ -12967,10 +12967,10 @@
         <v>Medium</v>
       </c>
       <c r="G209" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H209" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I209" t="str">
         <v>2025-08-28</v>
@@ -12991,7 +12991,7 @@
         <v>2025-11-12</v>
       </c>
       <c r="O209" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P209" t="str">
         <v>2/2</v>
@@ -13029,7 +13029,7 @@
         <v/>
       </c>
       <c r="H210" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I210" t="str">
         <v>2025-09-01</v>
@@ -13089,7 +13089,7 @@
         <v>Medium</v>
       </c>
       <c r="G211" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H211" t="str">
         <v/>
@@ -13113,7 +13113,7 @@
         <v>2025-10-13</v>
       </c>
       <c r="O211" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P211" t="str">
         <v>2/3</v>
@@ -13148,10 +13148,10 @@
         <v>Medium</v>
       </c>
       <c r="G212" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H212" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I212" t="str">
         <v>2025-09-01</v>
@@ -13214,10 +13214,10 @@
         <v>Medium</v>
       </c>
       <c r="G213" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H213" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I213" t="str">
         <v>2025-09-11</v>
@@ -13238,7 +13238,7 @@
         <v>2026-03-27</v>
       </c>
       <c r="O213" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P213" t="str">
         <v/>
@@ -13276,7 +13276,7 @@
         <v/>
       </c>
       <c r="H214" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I214" t="str">
         <v>2025-09-16</v>
@@ -13335,7 +13335,7 @@
         <v/>
       </c>
       <c r="H215" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I215" t="str">
         <v>2025-09-16</v>
@@ -13394,7 +13394,7 @@
         <v/>
       </c>
       <c r="H216" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I216" t="str">
         <v>2025-09-22</v>
@@ -13450,10 +13450,10 @@
         <v>Medium</v>
       </c>
       <c r="G217" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H217" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I217" t="str">
         <v>2025-09-23</v>
@@ -13474,7 +13474,7 @@
         <v>2025-11-10</v>
       </c>
       <c r="O217" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P217" t="str">
         <v/>
@@ -13509,10 +13509,10 @@
         <v>Medium</v>
       </c>
       <c r="G218" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H218" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I218" t="str">
         <v>2025-09-23</v>
@@ -13533,7 +13533,7 @@
         <v>2025-10-13</v>
       </c>
       <c r="O218" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P218" t="str">
         <v/>
@@ -13571,7 +13571,7 @@
         <v/>
       </c>
       <c r="H219" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I219" t="str">
         <v>2025-09-23</v>
@@ -13630,7 +13630,7 @@
         <v/>
       </c>
       <c r="H220" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I220" t="str">
         <v>2025-09-23</v>
@@ -13651,7 +13651,7 @@
         <v>2026-02-25</v>
       </c>
       <c r="O220" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P220" t="str">
         <v>2/3</v>
@@ -13695,7 +13695,7 @@
         <v/>
       </c>
       <c r="H221" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I221" t="str">
         <v>2025-09-23</v>
@@ -13716,7 +13716,7 @@
         <v>2025-11-24</v>
       </c>
       <c r="O221" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P221" t="str">
         <v/>
@@ -13757,7 +13757,7 @@
         <v/>
       </c>
       <c r="H222" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I222" t="str">
         <v>2025-09-24</v>
@@ -13778,7 +13778,7 @@
         <v>2025-10-13</v>
       </c>
       <c r="O222" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P222" t="str">
         <v/>
@@ -13813,10 +13813,10 @@
         <v>Medium</v>
       </c>
       <c r="G223" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H223" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I223" t="str">
         <v>2025-09-25</v>
@@ -13875,7 +13875,7 @@
         <v/>
       </c>
       <c r="H224" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I224" t="str">
         <v>2025-09-28</v>
@@ -13931,7 +13931,7 @@
         <v/>
       </c>
       <c r="H225" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I225" t="str">
         <v>2025-09-28</v>
@@ -13952,7 +13952,7 @@
         <v>2025-10-30</v>
       </c>
       <c r="O225" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P225" t="str">
         <v/>
@@ -13984,10 +13984,10 @@
         <v>Medium</v>
       </c>
       <c r="G226" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H226" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I226" t="str">
         <v>2025-10-07</v>
@@ -14008,7 +14008,7 @@
         <v>2025-11-10</v>
       </c>
       <c r="O226" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P226" t="str">
         <v/>
@@ -14040,10 +14040,10 @@
         <v>Medium</v>
       </c>
       <c r="G227" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H227" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I227" t="str">
         <v>2025-10-07</v>
@@ -14064,7 +14064,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O227" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P227" t="str">
         <v/>
@@ -14158,7 +14158,7 @@
         <v>Medium</v>
       </c>
       <c r="G229" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H229" t="str">
         <v/>
@@ -14217,7 +14217,7 @@
         <v>Medium</v>
       </c>
       <c r="G230" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H230" t="str">
         <v/>
@@ -14241,7 +14241,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O230" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P230" t="str">
         <v/>
@@ -14276,10 +14276,10 @@
         <v>Medium</v>
       </c>
       <c r="G231" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H231" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I231" t="str">
         <v>2025-10-30</v>
@@ -14300,7 +14300,7 @@
         <v>2026-01-08</v>
       </c>
       <c r="O231" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P231" t="str">
         <v/>
@@ -14335,10 +14335,10 @@
         <v>Urgent</v>
       </c>
       <c r="G232" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H232" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I232" t="str">
         <v>2025-10-30</v>
@@ -14359,7 +14359,7 @@
         <v>2026-02-12</v>
       </c>
       <c r="O232" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P232" t="str">
         <v/>
@@ -14394,10 +14394,10 @@
         <v>Medium</v>
       </c>
       <c r="G233" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H233" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I233" t="str">
         <v>2025-10-30</v>
@@ -14418,7 +14418,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="O233" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P233" t="str">
         <v/>
@@ -14453,10 +14453,10 @@
         <v>Medium</v>
       </c>
       <c r="G234" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H234" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I234" t="str">
         <v>2025-10-30</v>
@@ -14477,7 +14477,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O234" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P234" t="str">
         <v/>
@@ -14571,10 +14571,10 @@
         <v>Medium</v>
       </c>
       <c r="G236" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H236" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I236" t="str">
         <v>2025-11-11</v>
@@ -14595,7 +14595,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O236" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P236" t="str">
         <v/>
@@ -14630,10 +14630,10 @@
         <v>Medium</v>
       </c>
       <c r="G237" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H237" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I237" t="str">
         <v>2025-11-11</v>
@@ -14654,7 +14654,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O237" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P237" t="str">
         <v/>
@@ -14677,7 +14677,7 @@
         <v>Submission MRF_Multimedia Designer_Replacement_Req.By[Daniel Malau]</v>
       </c>
       <c r="C238" t="str">
-        <v>Order for Contract Sign &amp; ID dkk</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -14689,10 +14689,10 @@
         <v>Medium</v>
       </c>
       <c r="G238" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H238" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I238" t="str">
         <v>2025-11-11</v>
@@ -14713,7 +14713,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O238" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P238" t="str">
         <v/>
@@ -14748,10 +14748,10 @@
         <v>Medium</v>
       </c>
       <c r="G239" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H239" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I239" t="str">
         <v>2025-11-11</v>
@@ -14772,7 +14772,7 @@
         <v>2025-12-04</v>
       </c>
       <c r="O239" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="P239" t="str">
         <v/>
@@ -14807,10 +14807,10 @@
         <v>Medium</v>
       </c>
       <c r="G240" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H240" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I240" t="str">
         <v>2025-11-11</v>
@@ -14831,7 +14831,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O240" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P240" t="str">
         <v/>
@@ -14866,10 +14866,10 @@
         <v>Medium</v>
       </c>
       <c r="G241" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H241" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I241" t="str">
         <v>2025-11-12</v>
@@ -14890,7 +14890,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O241" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P241" t="str">
         <v/>
@@ -14925,10 +14925,10 @@
         <v>Medium</v>
       </c>
       <c r="G242" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H242" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I242" t="str">
         <v>2025-11-12</v>
@@ -14949,7 +14949,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O242" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P242" t="str">
         <v/>
@@ -14984,10 +14984,10 @@
         <v>Medium</v>
       </c>
       <c r="G243" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H243" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I243" t="str">
         <v>2025-11-12</v>
@@ -15008,7 +15008,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O243" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P243" t="str">
         <v/>
@@ -15031,7 +15031,7 @@
         <v>Reporter Money</v>
       </c>
       <c r="C244" t="str">
-        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+        <v>Offering</v>
       </c>
       <c r="D244" t="str">
         <v/>
@@ -15043,10 +15043,10 @@
         <v>Medium</v>
       </c>
       <c r="G244" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H244" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I244" t="str">
         <v>2025-11-12</v>
@@ -15102,10 +15102,10 @@
         <v>Medium</v>
       </c>
       <c r="G245" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H245" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I245" t="str">
         <v>2025-11-12</v>
@@ -15126,7 +15126,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O245" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P245" t="str">
         <v/>
@@ -15161,10 +15161,10 @@
         <v>Medium</v>
       </c>
       <c r="G246" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H246" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I246" t="str">
         <v>2025-11-12</v>
@@ -15185,7 +15185,7 @@
         <v>2026-02-25</v>
       </c>
       <c r="O246" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P246" t="str">
         <v/>
@@ -15220,10 +15220,10 @@
         <v>Medium</v>
       </c>
       <c r="G247" t="str">
-        <v>;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H247" t="str">
-        <v>Novinda Riski</v>
+        <v/>
       </c>
       <c r="I247" t="str">
         <v>2025-11-12</v>
@@ -15244,7 +15244,7 @@
         <v>2025-11-24</v>
       </c>
       <c r="O247" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P247" t="str">
         <v/>
@@ -15338,10 +15338,10 @@
         <v>Medium</v>
       </c>
       <c r="G249" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H249" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I249" t="str">
         <v>2025-11-12</v>
@@ -15362,7 +15362,7 @@
         <v>2026-03-17</v>
       </c>
       <c r="O249" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P249" t="str">
         <v/>
@@ -15385,22 +15385,22 @@
         <v>Reporter Nasional</v>
       </c>
       <c r="C250" t="str">
-        <v>Order for Contract Sign &amp; ID dkk</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D250" t="str">
         <v/>
       </c>
       <c r="E250" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F250" t="str">
         <v>Medium</v>
       </c>
       <c r="G250" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H250" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I250" t="str">
         <v>2025-11-19</v>
@@ -15418,7 +15418,7 @@
         <v>false</v>
       </c>
       <c r="N250" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O250" t="str">
         <v/>
@@ -15458,10 +15458,10 @@
         <v>Medium</v>
       </c>
       <c r="G251" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H251" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I251" t="str">
         <v>2025-11-24</v>
@@ -15482,7 +15482,7 @@
         <v>2026-03-17</v>
       </c>
       <c r="O251" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P251" t="str">
         <v/>
@@ -15517,10 +15517,10 @@
         <v>Medium</v>
       </c>
       <c r="G252" t="str">
-        <v>HR Development;Adelia Galuh H</v>
+        <v>;</v>
       </c>
       <c r="H252" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I252" t="str">
         <v>2025-11-28</v>
@@ -15541,7 +15541,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O252" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P252" t="str">
         <v/>
@@ -15576,10 +15576,10 @@
         <v>Medium</v>
       </c>
       <c r="G253" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H253" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I253" t="str">
         <v>2025-12-16</v>
@@ -15600,7 +15600,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O253" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P253" t="str">
         <v/>
@@ -15635,10 +15635,10 @@
         <v>Medium</v>
       </c>
       <c r="G254" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H254" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I254" t="str">
         <v>2025-12-16</v>
@@ -15659,7 +15659,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O254" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P254" t="str">
         <v/>
@@ -15694,10 +15694,10 @@
         <v>Medium</v>
       </c>
       <c r="G255" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H255" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I255" t="str">
         <v>2025-12-18</v>
@@ -15718,7 +15718,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O255" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P255" t="str">
         <v/>
@@ -15753,10 +15753,10 @@
         <v>Medium</v>
       </c>
       <c r="G256" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H256" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I256" t="str">
         <v>2025-12-18</v>
@@ -15777,7 +15777,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O256" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P256" t="str">
         <v/>
@@ -15800,7 +15800,7 @@
         <v>Associate Data Scientist</v>
       </c>
       <c r="C257" t="str">
-        <v>HR &amp; User Interview + Skill Test</v>
+        <v>HOLD</v>
       </c>
       <c r="D257" t="str">
         <v/>
@@ -15812,10 +15812,10 @@
         <v>Medium</v>
       </c>
       <c r="G257" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H257" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I257" t="str">
         <v>2025-12-18</v>
@@ -15859,22 +15859,22 @@
         <v>Data Engineer OVAL</v>
       </c>
       <c r="C258" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D258" t="str">
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>Not started</v>
+        <v>Completed</v>
       </c>
       <c r="F258" t="str">
         <v>Medium</v>
       </c>
       <c r="G258" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H258" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I258" t="str">
         <v>2025-12-18</v>
@@ -15892,10 +15892,10 @@
         <v>false</v>
       </c>
       <c r="N258" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="O258" t="str">
-        <v/>
+        <v>Netri Alia Rahmi</v>
       </c>
       <c r="P258" t="str">
         <v/>
@@ -15933,7 +15933,7 @@
         <v/>
       </c>
       <c r="H259" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I259" t="str">
         <v>2025-12-18</v>
@@ -15954,7 +15954,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O259" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P259" t="str">
         <v/>
@@ -15989,10 +15989,10 @@
         <v>Medium</v>
       </c>
       <c r="G260" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H260" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I260" t="str">
         <v>2025-12-18</v>
@@ -16013,7 +16013,7 @@
         <v>2025-12-18</v>
       </c>
       <c r="O260" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P260" t="str">
         <v/>
@@ -16048,10 +16048,10 @@
         <v>Medium</v>
       </c>
       <c r="G261" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H261" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I261" t="str">
         <v>2025-12-18</v>
@@ -16095,7 +16095,7 @@
         <v>Data Analyst OVAL = Data Scientist</v>
       </c>
       <c r="C262" t="str">
-        <v>HR &amp; User Interview + Skill Test</v>
+        <v>HOLD</v>
       </c>
       <c r="D262" t="str">
         <v/>
@@ -16107,10 +16107,10 @@
         <v>Medium</v>
       </c>
       <c r="G262" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H262" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I262" t="str">
         <v>2025-12-18</v>
@@ -16166,10 +16166,10 @@
         <v>Medium</v>
       </c>
       <c r="G263" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H263" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I263" t="str">
         <v>2025-12-18</v>
@@ -16225,10 +16225,10 @@
         <v>Medium</v>
       </c>
       <c r="G264" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H264" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I264" t="str">
         <v>2025-12-23</v>
@@ -16249,7 +16249,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O264" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P264" t="str">
         <v/>
@@ -16284,10 +16284,10 @@
         <v>Medium</v>
       </c>
       <c r="G265" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H265" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I265" t="str">
         <v>2025-12-23</v>
@@ -16343,10 +16343,10 @@
         <v>Medium</v>
       </c>
       <c r="G266" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H266" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I266" t="str">
         <v>2026-01-08</v>
@@ -16367,7 +16367,7 @@
         <v>2026-04-28</v>
       </c>
       <c r="O266" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P266" t="str">
         <v/>
@@ -16390,7 +16390,7 @@
         <v>Accounting KG Media</v>
       </c>
       <c r="C267" t="str">
-        <v>Order for Contract Sign &amp; ID dkk</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D267" t="str">
         <v/>
@@ -16402,10 +16402,10 @@
         <v>Medium</v>
       </c>
       <c r="G267" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H267" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I267" t="str">
         <v>2026-01-08</v>
@@ -16426,7 +16426,7 @@
         <v>2026-02-24</v>
       </c>
       <c r="O267" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P267" t="str">
         <v/>
@@ -16461,10 +16461,10 @@
         <v>Medium</v>
       </c>
       <c r="G268" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H268" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I268" t="str">
         <v>2026-01-08</v>
@@ -16485,7 +16485,7 @@
         <v>2026-02-02</v>
       </c>
       <c r="O268" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P268" t="str">
         <v/>
@@ -16520,10 +16520,10 @@
         <v>Medium</v>
       </c>
       <c r="G269" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H269" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I269" t="str">
         <v>2026-01-08</v>
@@ -16544,7 +16544,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O269" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P269" t="str">
         <v/>
@@ -16579,10 +16579,10 @@
         <v>Medium</v>
       </c>
       <c r="G270" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H270" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I270" t="str">
         <v>2026-01-15</v>
@@ -16603,7 +16603,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O270" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P270" t="str">
         <v/>
@@ -16638,10 +16638,10 @@
         <v>Medium</v>
       </c>
       <c r="G271" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H271" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I271" t="str">
         <v>2026-01-19</v>
@@ -16662,7 +16662,7 @@
         <v>2026-02-05</v>
       </c>
       <c r="O271" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P271" t="str">
         <v/>
@@ -16697,10 +16697,10 @@
         <v>Medium</v>
       </c>
       <c r="G272" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H272" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I272" t="str">
         <v>2026-01-27</v>
@@ -16721,7 +16721,7 @@
         <v>2026-02-09</v>
       </c>
       <c r="O272" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P272" t="str">
         <v/>
@@ -16756,10 +16756,10 @@
         <v>Medium</v>
       </c>
       <c r="G273" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H273" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I273" t="str">
         <v>2026-01-27</v>
@@ -16780,7 +16780,7 @@
         <v>2026-02-24</v>
       </c>
       <c r="O273" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P273" t="str">
         <v/>
@@ -16815,10 +16815,10 @@
         <v>Medium</v>
       </c>
       <c r="G274" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H274" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I274" t="str">
         <v>2026-01-27</v>
@@ -16874,10 +16874,10 @@
         <v>Medium</v>
       </c>
       <c r="G275" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H275" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I275" t="str">
         <v>2026-02-04</v>
@@ -16898,7 +16898,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O275" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P275" t="str">
         <v/>
@@ -16933,10 +16933,10 @@
         <v>Medium</v>
       </c>
       <c r="G276" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H276" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I276" t="str">
         <v>2026-02-04</v>
@@ -16957,7 +16957,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O276" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P276" t="str">
         <v/>
@@ -16992,10 +16992,10 @@
         <v>Medium</v>
       </c>
       <c r="G277" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H277" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I277" t="str">
         <v>2026-02-04</v>
@@ -17016,7 +17016,7 @@
         <v>2026-04-07</v>
       </c>
       <c r="O277" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P277" t="str">
         <v/>
@@ -17051,10 +17051,10 @@
         <v>Medium</v>
       </c>
       <c r="G278" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H278" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I278" t="str">
         <v>2026-02-05</v>
@@ -17075,7 +17075,7 @@
         <v>2026-02-16</v>
       </c>
       <c r="O278" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P278" t="str">
         <v/>
@@ -17110,10 +17110,10 @@
         <v>Medium</v>
       </c>
       <c r="G279" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H279" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I279" t="str">
         <v>2026-02-05</v>
@@ -17134,7 +17134,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O279" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P279" t="str">
         <v/>
@@ -17169,10 +17169,10 @@
         <v>Medium</v>
       </c>
       <c r="G280" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H280" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I280" t="str">
         <v>2026-02-05</v>
@@ -17228,10 +17228,10 @@
         <v>Medium</v>
       </c>
       <c r="G281" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H281" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I281" t="str">
         <v>2026-02-06</v>
@@ -17252,7 +17252,7 @@
         <v>2026-02-16</v>
       </c>
       <c r="O281" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P281" t="str">
         <v/>
@@ -17272,22 +17272,22 @@
         <v>Content Marketing Officer</v>
       </c>
       <c r="C282" t="str">
-        <v>Offering</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D282" t="str">
         <v/>
       </c>
       <c r="E282" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F282" t="str">
         <v>Medium</v>
       </c>
       <c r="G282" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H282" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I282" t="str">
         <v>2026-02-09</v>
@@ -17305,7 +17305,7 @@
         <v>false</v>
       </c>
       <c r="N282" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O282" t="str">
         <v/>
@@ -17343,10 +17343,10 @@
         <v>Medium</v>
       </c>
       <c r="G283" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H283" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I283" t="str">
         <v>2026-02-11</v>
@@ -17367,7 +17367,7 @@
         <v>2026-02-16</v>
       </c>
       <c r="O283" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="P283" t="str">
         <v/>
@@ -17402,10 +17402,10 @@
         <v>Medium</v>
       </c>
       <c r="G284" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H284" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I284" t="str">
         <v>2026-02-13</v>
@@ -17446,10 +17446,10 @@
         <v>uBoEFdesoEO9gl2E2YnMH8gAAhA5</v>
       </c>
       <c r="B285" t="str">
-        <v>Data Scanner (Unimind)</v>
+        <v>Freelance Data Scanner (Unimind)</v>
       </c>
       <c r="C285" t="str">
-        <v>In Progress (Untuk Task selain Recruitment Reguler)</v>
+        <v>HOLD</v>
       </c>
       <c r="D285" t="str">
         <v/>
@@ -17464,7 +17464,7 @@
         <v/>
       </c>
       <c r="H285" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I285" t="str">
         <v>2026-02-18</v>
@@ -17520,10 +17520,10 @@
         <v>Medium</v>
       </c>
       <c r="G286" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H286" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I286" t="str">
         <v>2026-02-19</v>
@@ -17579,10 +17579,10 @@
         <v>Medium</v>
       </c>
       <c r="G287" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H287" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I287" t="str">
         <v>2026-02-25</v>
@@ -17638,10 +17638,10 @@
         <v>Medium</v>
       </c>
       <c r="G288" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H288" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I288" t="str">
         <v>2026-03-09</v>
@@ -17685,7 +17685,7 @@
         <v>Reporter Megapolitan</v>
       </c>
       <c r="C289" t="str">
-        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+        <v>Offering</v>
       </c>
       <c r="D289" t="str">
         <v/>
@@ -17697,10 +17697,10 @@
         <v>Medium</v>
       </c>
       <c r="G289" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H289" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I289" t="str">
         <v>2026-03-09</v>
@@ -17756,10 +17756,10 @@
         <v>Medium</v>
       </c>
       <c r="G290" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H290" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I290" t="str">
         <v>2026-03-09</v>
@@ -17780,7 +17780,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O290" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P290" t="str">
         <v/>
@@ -17803,22 +17803,22 @@
         <v>Creative Marketing Product</v>
       </c>
       <c r="C291" t="str">
-        <v>Offering</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D291" t="str">
         <v/>
       </c>
       <c r="E291" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F291" t="str">
         <v>Medium</v>
       </c>
       <c r="G291" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H291" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I291" t="str">
         <v>2026-03-17</v>
@@ -17836,7 +17836,7 @@
         <v>false</v>
       </c>
       <c r="N291" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O291" t="str">
         <v/>
@@ -17868,16 +17868,16 @@
         <v/>
       </c>
       <c r="E292" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F292" t="str">
         <v>Medium</v>
       </c>
       <c r="G292" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H292" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I292" t="str">
         <v>2026-03-17</v>
@@ -17895,7 +17895,7 @@
         <v>false</v>
       </c>
       <c r="N292" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O292" t="str">
         <v/>
@@ -17933,10 +17933,10 @@
         <v>Medium</v>
       </c>
       <c r="G293" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H293" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I293" t="str">
         <v>2026-03-17</v>
@@ -17957,7 +17957,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="O293" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="P293" t="str">
         <v/>
@@ -17995,7 +17995,7 @@
         <v/>
       </c>
       <c r="H294" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I294" t="str">
         <v>2026-03-18</v>
@@ -18039,22 +18039,22 @@
         <v>Video Analyst</v>
       </c>
       <c r="C295" t="str">
-        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+        <v>Offering</v>
       </c>
       <c r="D295" t="str">
         <v/>
       </c>
       <c r="E295" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F295" t="str">
         <v>Medium</v>
       </c>
       <c r="G295" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H295" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I295" t="str">
         <v>2026-03-18</v>
@@ -18084,7 +18084,7 @@
         <v/>
       </c>
       <c r="R295" t="str">
-        <v/>
+        <v>KKWT</v>
       </c>
       <c r="S295" t="str">
         <v>Replace Nurdita (Research Marketing)</v>
@@ -18113,7 +18113,7 @@
         <v/>
       </c>
       <c r="H296" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I296" t="str">
         <v>2026-03-25</v>
@@ -18169,10 +18169,10 @@
         <v>Medium</v>
       </c>
       <c r="G297" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H297" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I297" t="str">
         <v>2026-03-27</v>
@@ -18216,7 +18216,7 @@
         <v>Sustainability Officer</v>
       </c>
       <c r="C298" t="str">
-        <v>HR &amp; User Interview + Skill Test</v>
+        <v>Order for Contract Sign &amp; ID dkk</v>
       </c>
       <c r="D298" t="str">
         <v/>
@@ -18228,10 +18228,10 @@
         <v>Medium</v>
       </c>
       <c r="G298" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H298" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I298" t="str">
         <v>2026-03-30</v>
@@ -18275,22 +18275,22 @@
         <v>Account Executive Pasangiklan</v>
       </c>
       <c r="C299" t="str">
-        <v>HR &amp; User Interview + Skill Test</v>
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
       </c>
       <c r="D299" t="str">
         <v/>
       </c>
       <c r="E299" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F299" t="str">
         <v>Medium</v>
       </c>
       <c r="G299" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="H299" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I299" t="str">
         <v>2026-03-31</v>
@@ -18308,7 +18308,7 @@
         <v>false</v>
       </c>
       <c r="N299" t="str">
-        <v/>
+        <v>2026-06-02</v>
       </c>
       <c r="O299" t="str">
         <v/>
@@ -18334,22 +18334,22 @@
         <v>Marcomm Officer (Brand Activation)</v>
       </c>
       <c r="C300" t="str">
-        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+        <v>Offering</v>
       </c>
       <c r="D300" t="str">
         <v/>
       </c>
       <c r="E300" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F300" t="str">
         <v>Medium</v>
       </c>
       <c r="G300" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H300" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I300" t="str">
         <v>2026-03-31</v>
@@ -18393,22 +18393,22 @@
         <v>Marcomm Officer (Partnership)</v>
       </c>
       <c r="C301" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>HR &amp; User Interview + Skill Test</v>
       </c>
       <c r="D301" t="str">
         <v/>
       </c>
       <c r="E301" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F301" t="str">
         <v>Medium</v>
       </c>
       <c r="G301" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H301" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I301" t="str">
         <v>2026-04-10</v>
@@ -18452,7 +18452,7 @@
         <v>Marcomm Officer (Content Strategist)</v>
       </c>
       <c r="C302" t="str">
-        <v>HR &amp; User Interview + Skill Test</v>
+        <v>Offering</v>
       </c>
       <c r="D302" t="str">
         <v/>
@@ -18464,10 +18464,10 @@
         <v>Medium</v>
       </c>
       <c r="G302" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H302" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I302" t="str">
         <v>2026-04-10</v>
@@ -18511,13 +18511,13 @@
         <v>Strategic Marketing Officer</v>
       </c>
       <c r="C303" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>Offering</v>
       </c>
       <c r="D303" t="str">
         <v/>
       </c>
       <c r="E303" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F303" t="str">
         <v>Medium</v>
@@ -18526,7 +18526,7 @@
         <v/>
       </c>
       <c r="H303" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I303" t="str">
         <v>2026-04-10</v>
@@ -18585,7 +18585,7 @@
         <v/>
       </c>
       <c r="H304" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I304" t="str">
         <v>2026-04-15</v>
@@ -18638,10 +18638,10 @@
         <v>Medium</v>
       </c>
       <c r="G305" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="H305" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I305" t="str">
         <v>2026-04-15</v>
@@ -18674,7 +18674,7 @@
         <v/>
       </c>
       <c r="S305" t="str">
-        <v>Replace Yogarta Awawa</v>
+        <v>Replace Yogarta Awawa - kontrak diselesaikan per 30 Juni 2026</v>
       </c>
     </row>
     <row r="306">
@@ -18685,13 +18685,13 @@
         <v>Reporter Money</v>
       </c>
       <c r="C306" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>HR &amp; User Interview + Skill Test</v>
       </c>
       <c r="D306" t="str">
         <v/>
       </c>
       <c r="E306" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F306" t="str">
         <v>Medium</v>
@@ -18700,7 +18700,7 @@
         <v/>
       </c>
       <c r="H306" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I306" t="str">
         <v>2026-04-15</v>
@@ -18744,13 +18744,13 @@
         <v>Content Marketing Specialist (Lative ads)</v>
       </c>
       <c r="C307" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>HR &amp; User Interview + Skill Test</v>
       </c>
       <c r="D307" t="str">
         <v/>
       </c>
       <c r="E307" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F307" t="str">
         <v>Medium</v>
@@ -18759,7 +18759,7 @@
         <v/>
       </c>
       <c r="H307" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I307" t="str">
         <v>2026-04-29</v>
@@ -18803,13 +18803,13 @@
         <v>Account Executive KCM</v>
       </c>
       <c r="C308" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>Offering</v>
       </c>
       <c r="D308" t="str">
         <v/>
       </c>
       <c r="E308" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F308" t="str">
         <v>Medium</v>
@@ -18818,7 +18818,7 @@
         <v/>
       </c>
       <c r="H308" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I308" t="str">
         <v>2026-04-29</v>
@@ -18862,13 +18862,13 @@
         <v>Account Executive-Gov</v>
       </c>
       <c r="C309" t="str">
-        <v>Offering</v>
+        <v>Order for Contract Sign &amp; ID dkk</v>
       </c>
       <c r="D309" t="str">
         <v/>
       </c>
       <c r="E309" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F309" t="str">
         <v>Medium</v>
@@ -18877,7 +18877,7 @@
         <v/>
       </c>
       <c r="H309" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I309" t="str">
         <v>2026-04-29</v>
@@ -18918,16 +18918,16 @@
         <v>8zRzjJvDNkyTeowbHtKizMgAA4Eh</v>
       </c>
       <c r="B310" t="str">
-        <v>Data Analyst Programmatic</v>
+        <v>Data Analyst Programmatic (Programmatic Officer)</v>
       </c>
       <c r="C310" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>HR &amp; User Interview + Skill Test</v>
       </c>
       <c r="D310" t="str">
         <v/>
       </c>
       <c r="E310" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F310" t="str">
         <v>Medium</v>
@@ -18936,7 +18936,7 @@
         <v/>
       </c>
       <c r="H310" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I310" t="str">
         <v>2026-04-29</v>
@@ -18969,7 +18969,7 @@
         <v>Freelance</v>
       </c>
       <c r="S310" t="str">
-        <v>Additional</v>
+        <v>Replace cuti lahiran mba mia 3 bulan</v>
       </c>
     </row>
     <row r="311">
@@ -18980,13 +18980,13 @@
         <v>Finance Intern</v>
       </c>
       <c r="C311" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
       </c>
       <c r="D311" t="str">
         <v/>
       </c>
       <c r="E311" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F311" t="str">
         <v>Medium</v>
@@ -18995,7 +18995,7 @@
         <v/>
       </c>
       <c r="H311" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I311" t="str">
         <v>2026-04-29</v>
@@ -19036,16 +19036,16 @@
         <v>ZZsASLewukqZ-kLzPHjTJcgAORtm</v>
       </c>
       <c r="B312" t="str">
-        <v>Sosial media distributor intern</v>
+        <v>Social Media Distribution Intern</v>
       </c>
       <c r="C312" t="str">
-        <v>Backlog (Employee Req Form)</v>
+        <v>Offering</v>
       </c>
       <c r="D312" t="str">
         <v/>
       </c>
       <c r="E312" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F312" t="str">
         <v>Medium</v>
@@ -19054,7 +19054,7 @@
         <v/>
       </c>
       <c r="H312" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I312" t="str">
         <v>2026-04-29</v>
@@ -19085,6 +19085,9 @@
       </c>
       <c r="R312" t="str">
         <v/>
+      </c>
+      <c r="S312" t="str">
+        <v>Replace Amirah (22 Mei) &amp; Tiara (31 Mei)</v>
       </c>
     </row>
     <row r="313">
@@ -19095,7 +19098,7 @@
         <v>Content Creator Intern (Lative ads)</v>
       </c>
       <c r="C313" t="str">
-        <v>HR &amp; User Interview + Skill Test</v>
+        <v>Offering</v>
       </c>
       <c r="D313" t="str">
         <v/>
@@ -19110,7 +19113,7 @@
         <v/>
       </c>
       <c r="H313" t="str">
-        <v>HR Development</v>
+        <v/>
       </c>
       <c r="I313" t="str">
         <v>2026-04-29</v>
@@ -19151,10 +19154,10 @@
         <v>4dJSRStxWke8uPeGLm_5_8gAOomH</v>
       </c>
       <c r="B314" t="str">
-        <v>Ad Ops Officer</v>
+        <v>Ad Ops Officer (KCM)</v>
       </c>
       <c r="C314" t="str">
-        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+        <v>HR &amp; User Interview + Skill Test</v>
       </c>
       <c r="D314" t="str">
         <v/>
@@ -19169,7 +19172,7 @@
         <v/>
       </c>
       <c r="H314" t="str">
-        <v>Adelia Galuh H</v>
+        <v/>
       </c>
       <c r="I314" t="str">
         <v>2026-04-29</v>
@@ -19199,22 +19202,727 @@
         <v/>
       </c>
       <c r="R314" t="str">
-        <v/>
+        <v>Replacement</v>
       </c>
       <c r="S314" t="str">
         <v>Replace Achmad Ifan</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>ISKW0vFUNU2p0L0BRllxasgAEggk</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Marketing Package Support</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Order for Contract Sign &amp; ID dkk</v>
+      </c>
+      <c r="D315" t="str">
+        <v/>
+      </c>
+      <c r="E315" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F315" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G315" t="str">
+        <v/>
+      </c>
+      <c r="H315" t="str">
+        <v/>
+      </c>
+      <c r="I315" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="J315" t="str">
+        <v/>
+      </c>
+      <c r="K315" t="str">
+        <v/>
+      </c>
+      <c r="L315" t="str">
+        <v/>
+      </c>
+      <c r="M315" t="str">
+        <v>false</v>
+      </c>
+      <c r="N315" t="str">
+        <v/>
+      </c>
+      <c r="O315" t="str">
+        <v/>
+      </c>
+      <c r="P315" t="str">
+        <v/>
+      </c>
+      <c r="Q315" t="str">
+        <v/>
+      </c>
+      <c r="R315" t="str">
+        <v/>
+      </c>
+      <c r="S315" t="str">
+        <v>Replace Rania</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>TWoBx_hqbkOwLh1Dfjy6JsgAAkhv</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Video Journalist</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+      </c>
+      <c r="D316" t="str">
+        <v/>
+      </c>
+      <c r="E316" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F316" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G316" t="str">
+        <v/>
+      </c>
+      <c r="H316" t="str">
+        <v/>
+      </c>
+      <c r="I316" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="J316" t="str">
+        <v/>
+      </c>
+      <c r="K316" t="str">
+        <v/>
+      </c>
+      <c r="L316" t="str">
+        <v/>
+      </c>
+      <c r="M316" t="str">
+        <v>false</v>
+      </c>
+      <c r="N316" t="str">
+        <v/>
+      </c>
+      <c r="O316" t="str">
+        <v/>
+      </c>
+      <c r="P316" t="str">
+        <v/>
+      </c>
+      <c r="Q316" t="str">
+        <v/>
+      </c>
+      <c r="R316" t="str">
+        <v/>
+      </c>
+      <c r="S316" t="str">
+        <v>Replace Rizky Syahrial</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>L-luduLfPkSzM3PLp-omjsgAF9nv</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Finance AR KG Media</v>
+      </c>
+      <c r="C317" t="str">
+        <v>HR &amp; User Interview + Skill Test</v>
+      </c>
+      <c r="D317" t="str">
+        <v/>
+      </c>
+      <c r="E317" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F317" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G317" t="str">
+        <v/>
+      </c>
+      <c r="H317" t="str">
+        <v/>
+      </c>
+      <c r="I317" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="J317" t="str">
+        <v/>
+      </c>
+      <c r="K317" t="str">
+        <v/>
+      </c>
+      <c r="L317" t="str">
+        <v/>
+      </c>
+      <c r="M317" t="str">
+        <v>false</v>
+      </c>
+      <c r="N317" t="str">
+        <v/>
+      </c>
+      <c r="O317" t="str">
+        <v/>
+      </c>
+      <c r="P317" t="str">
+        <v/>
+      </c>
+      <c r="Q317" t="str">
+        <v/>
+      </c>
+      <c r="R317" t="str">
+        <v/>
+      </c>
+      <c r="S317" t="str">
+        <v>Replace Aurilih</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>ogTM-LAJKEiUG2RuSp31yMgACFUc</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Creative Designer</v>
+      </c>
+      <c r="C318" t="str">
+        <v>HR &amp; User Interview + Skill Test</v>
+      </c>
+      <c r="D318" t="str">
+        <v/>
+      </c>
+      <c r="E318" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F318" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G318" t="str">
+        <v/>
+      </c>
+      <c r="H318" t="str">
+        <v/>
+      </c>
+      <c r="I318" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="J318" t="str">
+        <v/>
+      </c>
+      <c r="K318" t="str">
+        <v/>
+      </c>
+      <c r="L318" t="str">
+        <v/>
+      </c>
+      <c r="M318" t="str">
+        <v>false</v>
+      </c>
+      <c r="N318" t="str">
+        <v/>
+      </c>
+      <c r="O318" t="str">
+        <v/>
+      </c>
+      <c r="P318" t="str">
+        <v/>
+      </c>
+      <c r="Q318" t="str">
+        <v/>
+      </c>
+      <c r="R318" t="str">
+        <v>Freelance;Replacement</v>
+      </c>
+      <c r="S318" t="str">
+        <v>Replace Ridho</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>nNl-hAIbd0m07BT7kGN8TsgABkXI</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Account Executive KCM</v>
+      </c>
+      <c r="C319" t="str">
+        <v>Backlog (Employee Req Form)</v>
+      </c>
+      <c r="D319" t="str">
+        <v/>
+      </c>
+      <c r="E319" t="str">
+        <v>Not started</v>
+      </c>
+      <c r="F319" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G319" t="str">
+        <v/>
+      </c>
+      <c r="H319" t="str">
+        <v/>
+      </c>
+      <c r="I319" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="J319" t="str">
+        <v/>
+      </c>
+      <c r="K319" t="str">
+        <v/>
+      </c>
+      <c r="L319" t="str">
+        <v/>
+      </c>
+      <c r="M319" t="str">
+        <v>false</v>
+      </c>
+      <c r="N319" t="str">
+        <v/>
+      </c>
+      <c r="O319" t="str">
+        <v/>
+      </c>
+      <c r="P319" t="str">
+        <v/>
+      </c>
+      <c r="Q319" t="str">
+        <v/>
+      </c>
+      <c r="R319" t="str">
+        <v/>
+      </c>
+      <c r="S319" t="str">
+        <v>Replace Bangkit yang digeser ke tim mas tomi</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>4ErHzmlDxUeTwJhUWrFdjsgABfo2</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Account Executive KCM</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Backlog (Employee Req Form)</v>
+      </c>
+      <c r="D320" t="str">
+        <v/>
+      </c>
+      <c r="E320" t="str">
+        <v>Not started</v>
+      </c>
+      <c r="F320" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G320" t="str">
+        <v/>
+      </c>
+      <c r="H320" t="str">
+        <v/>
+      </c>
+      <c r="I320" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J320" t="str">
+        <v/>
+      </c>
+      <c r="K320" t="str">
+        <v/>
+      </c>
+      <c r="L320" t="str">
+        <v/>
+      </c>
+      <c r="M320" t="str">
+        <v>false</v>
+      </c>
+      <c r="N320" t="str">
+        <v/>
+      </c>
+      <c r="O320" t="str">
+        <v/>
+      </c>
+      <c r="P320" t="str">
+        <v/>
+      </c>
+      <c r="Q320" t="str">
+        <v/>
+      </c>
+      <c r="R320" t="str">
+        <v/>
+      </c>
+      <c r="S320" t="str">
+        <v>Replace Gito pindah ke tim Mba Tita</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>bzb3uAzmq0yifTDVYXs5SMgADLCT</v>
+      </c>
+      <c r="B321" t="str">
+        <v>MUA Intern</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Offering</v>
+      </c>
+      <c r="D321" t="str">
+        <v/>
+      </c>
+      <c r="E321" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F321" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G321" t="str">
+        <v/>
+      </c>
+      <c r="H321" t="str">
+        <v/>
+      </c>
+      <c r="I321" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="J321" t="str">
+        <v/>
+      </c>
+      <c r="K321" t="str">
+        <v/>
+      </c>
+      <c r="L321" t="str">
+        <v/>
+      </c>
+      <c r="M321" t="str">
+        <v>false</v>
+      </c>
+      <c r="N321" t="str">
+        <v/>
+      </c>
+      <c r="O321" t="str">
+        <v/>
+      </c>
+      <c r="P321" t="str">
+        <v/>
+      </c>
+      <c r="Q321" t="str">
+        <v/>
+      </c>
+      <c r="R321" t="str">
+        <v>Intern-Paid</v>
+      </c>
+      <c r="S321" t="str">
+        <v>Melanjutkan intern a/n Syifa dari Maganghub Kemnaker Batch 2</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>YXJn_d_IPE6nQ3WawHh_r8gABqZK</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Intern Employer Branding KG Media</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Approval Circular &amp; Review (Paralel Screening CV)</v>
+      </c>
+      <c r="D322" t="str">
+        <v/>
+      </c>
+      <c r="E322" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F322" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G322" t="str">
+        <v/>
+      </c>
+      <c r="H322" t="str">
+        <v/>
+      </c>
+      <c r="I322" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="J322" t="str">
+        <v/>
+      </c>
+      <c r="K322" t="str">
+        <v/>
+      </c>
+      <c r="L322" t="str">
+        <v/>
+      </c>
+      <c r="M322" t="str">
+        <v>false</v>
+      </c>
+      <c r="N322" t="str">
+        <v/>
+      </c>
+      <c r="O322" t="str">
+        <v/>
+      </c>
+      <c r="P322" t="str">
+        <v/>
+      </c>
+      <c r="Q322" t="str">
+        <v/>
+      </c>
+      <c r="R322" t="str">
+        <v>Unpaid</v>
+      </c>
+      <c r="S322" t="str">
+        <v>buat di tim Lestari KG Media (additional)</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>I8e0xK_4WU66_3ycDNM8NcgAHn2h</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Digital Archivist Intern</v>
+      </c>
+      <c r="C323" t="str">
+        <v>HR &amp; User Interview + Skill Test</v>
+      </c>
+      <c r="D323" t="str">
+        <v/>
+      </c>
+      <c r="E323" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F323" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G323" t="str">
+        <v/>
+      </c>
+      <c r="H323" t="str">
+        <v/>
+      </c>
+      <c r="I323" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="J323" t="str">
+        <v/>
+      </c>
+      <c r="K323" t="str">
+        <v/>
+      </c>
+      <c r="L323" t="str">
+        <v/>
+      </c>
+      <c r="M323" t="str">
+        <v>false</v>
+      </c>
+      <c r="N323" t="str">
+        <v/>
+      </c>
+      <c r="O323" t="str">
+        <v/>
+      </c>
+      <c r="P323" t="str">
+        <v/>
+      </c>
+      <c r="Q323" t="str">
+        <v/>
+      </c>
+      <c r="R323" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>cPz89enrUEKB0B4vnLoMEMgAL3j9</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Account Executive Pasangiklan</v>
+      </c>
+      <c r="C324" t="str">
+        <v>HR &amp; User Interview + Skill Test</v>
+      </c>
+      <c r="D324" t="str">
+        <v/>
+      </c>
+      <c r="E324" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F324" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G324" t="str">
+        <v/>
+      </c>
+      <c r="H324" t="str">
+        <v/>
+      </c>
+      <c r="I324" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="J324" t="str">
+        <v/>
+      </c>
+      <c r="K324" t="str">
+        <v/>
+      </c>
+      <c r="L324" t="str">
+        <v/>
+      </c>
+      <c r="M324" t="str">
+        <v>false</v>
+      </c>
+      <c r="N324" t="str">
+        <v/>
+      </c>
+      <c r="O324" t="str">
+        <v/>
+      </c>
+      <c r="P324" t="str">
+        <v/>
+      </c>
+      <c r="Q324" t="str">
+        <v/>
+      </c>
+      <c r="R324" t="str">
+        <v>KKWT</v>
+      </c>
+      <c r="S324" t="str">
+        <v>Replace Moza</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>LKpiEsrzb0CetoK8u550KsgAONAA</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Host &amp; Creative</v>
+      </c>
+      <c r="C325" t="str">
+        <v>Sudah Sign Contract Lanjut Onboarding</v>
+      </c>
+      <c r="D325" t="str">
+        <v/>
+      </c>
+      <c r="E325" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F325" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G325" t="str">
+        <v/>
+      </c>
+      <c r="H325" t="str">
+        <v/>
+      </c>
+      <c r="I325" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="J325" t="str">
+        <v/>
+      </c>
+      <c r="K325" t="str">
+        <v/>
+      </c>
+      <c r="L325" t="str">
+        <v/>
+      </c>
+      <c r="M325" t="str">
+        <v>false</v>
+      </c>
+      <c r="N325" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="O325" t="str">
+        <v/>
+      </c>
+      <c r="P325" t="str">
+        <v/>
+      </c>
+      <c r="Q325" t="str">
+        <v/>
+      </c>
+      <c r="R325" t="str">
+        <v/>
+      </c>
+      <c r="S325" t="str">
+        <v>Additional - alih status Rega dari freelance ke KKWT</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>a6kDTvMIX0eZhPGvFZSETMgAJ_DU</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Host &amp; Creative</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Offering</v>
+      </c>
+      <c r="D326" t="str">
+        <v/>
+      </c>
+      <c r="E326" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F326" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v/>
+      </c>
+      <c r="I326" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="J326" t="str">
+        <v/>
+      </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
+      <c r="L326" t="str">
+        <v/>
+      </c>
+      <c r="M326" t="str">
+        <v>false</v>
+      </c>
+      <c r="N326" t="str">
+        <v/>
+      </c>
+      <c r="O326" t="str">
+        <v/>
+      </c>
+      <c r="P326" t="str">
+        <v/>
+      </c>
+      <c r="Q326" t="str">
+        <v/>
+      </c>
+      <c r="R326" t="str">
+        <v/>
+      </c>
+      <c r="S326" t="str">
+        <v>Replace Jessica Emmanuela -&gt; pindah sales government</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S314"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S326"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S314"/>
+  <dimension ref="A1:S326"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -26437,13 +27145,13 @@
         <v>Product Designer</v>
       </c>
       <c r="C121" t="str">
-        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D121" t="str">
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F121" t="str">
         <v>Important</v>
@@ -26470,10 +27178,10 @@
         <v>false</v>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O121" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="P121" t="str">
         <v/>
@@ -29418,7 +30126,7 @@
         <v>Sr. Strategic Planner StratX (Grid)</v>
       </c>
       <c r="C171" t="str">
-        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
       </c>
       <c r="D171" t="str">
         <v/>
@@ -31493,13 +32201,13 @@
         <v>Product Designer = Video Content Creator AI</v>
       </c>
       <c r="C205" t="str">
-        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D205" t="str">
         <v/>
       </c>
       <c r="E205" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F205" t="str">
         <v>Medium</v>
@@ -31526,10 +32234,10 @@
         <v>false</v>
       </c>
       <c r="N205" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="O205" t="str">
-        <v/>
+        <v>bea4b736-604e-4c3c-9844-ec5583740132</v>
       </c>
       <c r="P205" t="str">
         <v/>
@@ -33451,7 +34159,7 @@
         <v>Submission MRF_Multimedia Designer_Replacement_Req.By[Daniel Malau]</v>
       </c>
       <c r="C238" t="str">
-        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D238" t="str">
         <v/>
@@ -33805,7 +34513,7 @@
         <v>Reporter Money</v>
       </c>
       <c r="C244" t="str">
-        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D244" t="str">
         <v/>
@@ -34159,13 +34867,13 @@
         <v>Reporter Nasional</v>
       </c>
       <c r="C250" t="str">
-        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D250" t="str">
         <v/>
       </c>
       <c r="E250" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F250" t="str">
         <v>Medium</v>
@@ -34192,10 +34900,10 @@
         <v>false</v>
       </c>
       <c r="N250" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O250" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="P250" t="str">
         <v/>
@@ -34574,7 +35282,7 @@
         <v>Associate Data Scientist</v>
       </c>
       <c r="C257" t="str">
-        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+        <v>PB60MephskWnUj5KAlYslsgAIqNQ</v>
       </c>
       <c r="D257" t="str">
         <v/>
@@ -34633,13 +35341,13 @@
         <v>Data Engineer OVAL</v>
       </c>
       <c r="C258" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D258" t="str">
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>Not started</v>
+        <v>Completed</v>
       </c>
       <c r="F258" t="str">
         <v>Medium</v>
@@ -34666,10 +35374,10 @@
         <v>false</v>
       </c>
       <c r="N258" t="str">
-        <v/>
+        <v>2026-05-25</v>
       </c>
       <c r="O258" t="str">
-        <v/>
+        <v>bea4b736-604e-4c3c-9844-ec5583740132</v>
       </c>
       <c r="P258" t="str">
         <v/>
@@ -34869,7 +35577,7 @@
         <v>Data Analyst OVAL = Data Scientist</v>
       </c>
       <c r="C262" t="str">
-        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+        <v>PB60MephskWnUj5KAlYslsgAIqNQ</v>
       </c>
       <c r="D262" t="str">
         <v/>
@@ -35164,7 +35872,7 @@
         <v>Accounting KG Media</v>
       </c>
       <c r="C267" t="str">
-        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D267" t="str">
         <v/>
@@ -36046,13 +36754,13 @@
         <v>Content Marketing Officer</v>
       </c>
       <c r="C282" t="str">
-        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D282" t="str">
         <v/>
       </c>
       <c r="E282" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F282" t="str">
         <v>Medium</v>
@@ -36079,10 +36787,10 @@
         <v>false</v>
       </c>
       <c r="N282" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O282" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="P282" t="str">
         <v/>
@@ -36220,10 +36928,10 @@
         <v>uBoEFdesoEO9gl2E2YnMH8gAAhA5</v>
       </c>
       <c r="B285" t="str">
-        <v>Data Scanner (Unimind)</v>
+        <v>Freelance Data Scanner (Unimind)</v>
       </c>
       <c r="C285" t="str">
-        <v>tmoBkXOwC0-VxbVJW4TOHsgAJ7KY</v>
+        <v>PB60MephskWnUj5KAlYslsgAIqNQ</v>
       </c>
       <c r="D285" t="str">
         <v/>
@@ -36459,7 +37167,7 @@
         <v>Reporter Megapolitan</v>
       </c>
       <c r="C289" t="str">
-        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D289" t="str">
         <v/>
@@ -36577,13 +37285,13 @@
         <v>Creative Marketing Product</v>
       </c>
       <c r="C291" t="str">
-        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D291" t="str">
         <v/>
       </c>
       <c r="E291" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F291" t="str">
         <v>Medium</v>
@@ -36610,10 +37318,10 @@
         <v>false</v>
       </c>
       <c r="N291" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O291" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="P291" t="str">
         <v/>
@@ -36642,7 +37350,7 @@
         <v/>
       </c>
       <c r="E292" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F292" t="str">
         <v>Medium</v>
@@ -36669,10 +37377,10 @@
         <v>false</v>
       </c>
       <c r="N292" t="str">
-        <v/>
+        <v>2026-05-13</v>
       </c>
       <c r="O292" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="P292" t="str">
         <v/>
@@ -36813,13 +37521,13 @@
         <v>Video Analyst</v>
       </c>
       <c r="C295" t="str">
-        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D295" t="str">
         <v/>
       </c>
       <c r="E295" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F295" t="str">
         <v>Medium</v>
@@ -36858,7 +37566,7 @@
         <v/>
       </c>
       <c r="R295" t="str">
-        <v/>
+        <v>KKWT</v>
       </c>
       <c r="S295" t="str">
         <v>Replace Nurdita (Research Marketing)</v>
@@ -36990,7 +37698,7 @@
         <v>Sustainability Officer</v>
       </c>
       <c r="C298" t="str">
-        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
       </c>
       <c r="D298" t="str">
         <v/>
@@ -37049,13 +37757,13 @@
         <v>Account Executive Pasangiklan</v>
       </c>
       <c r="C299" t="str">
-        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
       </c>
       <c r="D299" t="str">
         <v/>
       </c>
       <c r="E299" t="str">
-        <v>In progress</v>
+        <v>Completed</v>
       </c>
       <c r="F299" t="str">
         <v>Medium</v>
@@ -37082,10 +37790,10 @@
         <v>false</v>
       </c>
       <c r="N299" t="str">
-        <v/>
+        <v>2026-06-02</v>
       </c>
       <c r="O299" t="str">
-        <v/>
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
       </c>
       <c r="P299" t="str">
         <v/>
@@ -37108,13 +37816,13 @@
         <v>Marcomm Officer (Brand Activation)</v>
       </c>
       <c r="C300" t="str">
-        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D300" t="str">
         <v/>
       </c>
       <c r="E300" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F300" t="str">
         <v>Medium</v>
@@ -37167,13 +37875,13 @@
         <v>Marcomm Officer (Partnership)</v>
       </c>
       <c r="C301" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
       </c>
       <c r="D301" t="str">
         <v/>
       </c>
       <c r="E301" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F301" t="str">
         <v>Medium</v>
@@ -37226,7 +37934,7 @@
         <v>Marcomm Officer (Content Strategist)</v>
       </c>
       <c r="C302" t="str">
-        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D302" t="str">
         <v/>
@@ -37285,13 +37993,13 @@
         <v>Strategic Marketing Officer</v>
       </c>
       <c r="C303" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D303" t="str">
         <v/>
       </c>
       <c r="E303" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F303" t="str">
         <v>Medium</v>
@@ -37448,7 +38156,7 @@
         <v/>
       </c>
       <c r="S305" t="str">
-        <v>Replace Yogarta Awawa</v>
+        <v>Replace Yogarta Awawa - kontrak diselesaikan per 30 Juni 2026</v>
       </c>
     </row>
     <row r="306">
@@ -37459,13 +38167,13 @@
         <v>Reporter Money</v>
       </c>
       <c r="C306" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
       </c>
       <c r="D306" t="str">
         <v/>
       </c>
       <c r="E306" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F306" t="str">
         <v>Medium</v>
@@ -37518,13 +38226,13 @@
         <v>Content Marketing Specialist (Lative ads)</v>
       </c>
       <c r="C307" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
       </c>
       <c r="D307" t="str">
         <v/>
       </c>
       <c r="E307" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F307" t="str">
         <v>Medium</v>
@@ -37577,19 +38285,19 @@
         <v>Account Executive KCM</v>
       </c>
       <c r="C308" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D308" t="str">
         <v/>
       </c>
       <c r="E308" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F308" t="str">
         <v>Medium</v>
       </c>
       <c r="G308" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="H308" t="str">
         <v>00672709-9ae7-4622-852f-f212507435f4</v>
@@ -37636,13 +38344,13 @@
         <v>Account Executive-Gov</v>
       </c>
       <c r="C309" t="str">
-        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
       </c>
       <c r="D309" t="str">
         <v/>
       </c>
       <c r="E309" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F309" t="str">
         <v>Medium</v>
@@ -37692,16 +38400,16 @@
         <v>8zRzjJvDNkyTeowbHtKizMgAA4Eh</v>
       </c>
       <c r="B310" t="str">
-        <v>Data Analyst Programmatic</v>
+        <v>Data Analyst Programmatic (Programmatic Officer)</v>
       </c>
       <c r="C310" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
       </c>
       <c r="D310" t="str">
         <v/>
       </c>
       <c r="E310" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F310" t="str">
         <v>Medium</v>
@@ -37743,7 +38451,7 @@
         <v>Freelance</v>
       </c>
       <c r="S310" t="str">
-        <v>Additional</v>
+        <v>Replace cuti lahiran mba mia 3 bulan</v>
       </c>
     </row>
     <row r="311">
@@ -37754,19 +38462,19 @@
         <v>Finance Intern</v>
       </c>
       <c r="C311" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
       </c>
       <c r="D311" t="str">
         <v/>
       </c>
       <c r="E311" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F311" t="str">
         <v>Medium</v>
       </c>
       <c r="G311" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="H311" t="str">
         <v>00672709-9ae7-4622-852f-f212507435f4</v>
@@ -37810,22 +38518,22 @@
         <v>ZZsASLewukqZ-kLzPHjTJcgAORtm</v>
       </c>
       <c r="B312" t="str">
-        <v>Sosial media distributor intern</v>
+        <v>Social Media Distribution Intern</v>
       </c>
       <c r="C312" t="str">
-        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D312" t="str">
         <v/>
       </c>
       <c r="E312" t="str">
-        <v>Not started</v>
+        <v>In progress</v>
       </c>
       <c r="F312" t="str">
         <v>Medium</v>
       </c>
       <c r="G312" t="str">
-        <v/>
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
       </c>
       <c r="H312" t="str">
         <v>00672709-9ae7-4622-852f-f212507435f4</v>
@@ -37859,6 +38567,9 @@
       </c>
       <c r="R312" t="str">
         <v/>
+      </c>
+      <c r="S312" t="str">
+        <v>Replace Amirah (22 Mei) &amp; Tiara (31 Mei)</v>
       </c>
     </row>
     <row r="313">
@@ -37869,7 +38580,7 @@
         <v>Content Creator Intern (Lative ads)</v>
       </c>
       <c r="C313" t="str">
-        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
       </c>
       <c r="D313" t="str">
         <v/>
@@ -37925,10 +38636,10 @@
         <v>4dJSRStxWke8uPeGLm_5_8gAOomH</v>
       </c>
       <c r="B314" t="str">
-        <v>Ad Ops Officer</v>
+        <v>Ad Ops Officer (KCM)</v>
       </c>
       <c r="C314" t="str">
-        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
       </c>
       <c r="D314" t="str">
         <v/>
@@ -37973,15 +38684,720 @@
         <v/>
       </c>
       <c r="R314" t="str">
-        <v/>
+        <v>Replacement</v>
       </c>
       <c r="S314" t="str">
         <v>Replace Achmad Ifan</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>ISKW0vFUNU2p0L0BRllxasgAEggk</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Marketing Package Support</v>
+      </c>
+      <c r="C315" t="str">
+        <v>QCIqDrw-L02X8Bk1hyqLm8gAJ6q4</v>
+      </c>
+      <c r="D315" t="str">
+        <v/>
+      </c>
+      <c r="E315" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F315" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G315" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="H315" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I315" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="J315" t="str">
+        <v/>
+      </c>
+      <c r="K315" t="str">
+        <v/>
+      </c>
+      <c r="L315" t="str">
+        <v/>
+      </c>
+      <c r="M315" t="str">
+        <v>false</v>
+      </c>
+      <c r="N315" t="str">
+        <v/>
+      </c>
+      <c r="O315" t="str">
+        <v/>
+      </c>
+      <c r="P315" t="str">
+        <v/>
+      </c>
+      <c r="Q315" t="str">
+        <v/>
+      </c>
+      <c r="R315" t="str">
+        <v/>
+      </c>
+      <c r="S315" t="str">
+        <v>Replace Rania</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>TWoBx_hqbkOwLh1Dfjy6JsgAAkhv</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Video Journalist</v>
+      </c>
+      <c r="C316" t="str">
+        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+      </c>
+      <c r="D316" t="str">
+        <v/>
+      </c>
+      <c r="E316" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F316" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G316" t="str">
+        <v/>
+      </c>
+      <c r="H316" t="str">
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
+      </c>
+      <c r="I316" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="J316" t="str">
+        <v/>
+      </c>
+      <c r="K316" t="str">
+        <v/>
+      </c>
+      <c r="L316" t="str">
+        <v/>
+      </c>
+      <c r="M316" t="str">
+        <v>false</v>
+      </c>
+      <c r="N316" t="str">
+        <v/>
+      </c>
+      <c r="O316" t="str">
+        <v/>
+      </c>
+      <c r="P316" t="str">
+        <v/>
+      </c>
+      <c r="Q316" t="str">
+        <v/>
+      </c>
+      <c r="R316" t="str">
+        <v/>
+      </c>
+      <c r="S316" t="str">
+        <v>Replace Rizky Syahrial</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>L-luduLfPkSzM3PLp-omjsgAF9nv</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Finance AR KG Media</v>
+      </c>
+      <c r="C317" t="str">
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+      </c>
+      <c r="D317" t="str">
+        <v/>
+      </c>
+      <c r="E317" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F317" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G317" t="str">
+        <v/>
+      </c>
+      <c r="H317" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I317" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="J317" t="str">
+        <v/>
+      </c>
+      <c r="K317" t="str">
+        <v/>
+      </c>
+      <c r="L317" t="str">
+        <v/>
+      </c>
+      <c r="M317" t="str">
+        <v>false</v>
+      </c>
+      <c r="N317" t="str">
+        <v/>
+      </c>
+      <c r="O317" t="str">
+        <v/>
+      </c>
+      <c r="P317" t="str">
+        <v/>
+      </c>
+      <c r="Q317" t="str">
+        <v/>
+      </c>
+      <c r="R317" t="str">
+        <v/>
+      </c>
+      <c r="S317" t="str">
+        <v>Replace Aurilih</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>ogTM-LAJKEiUG2RuSp31yMgACFUc</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Creative Designer</v>
+      </c>
+      <c r="C318" t="str">
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+      </c>
+      <c r="D318" t="str">
+        <v/>
+      </c>
+      <c r="E318" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F318" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G318" t="str">
+        <v/>
+      </c>
+      <c r="H318" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I318" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="J318" t="str">
+        <v/>
+      </c>
+      <c r="K318" t="str">
+        <v/>
+      </c>
+      <c r="L318" t="str">
+        <v/>
+      </c>
+      <c r="M318" t="str">
+        <v>false</v>
+      </c>
+      <c r="N318" t="str">
+        <v/>
+      </c>
+      <c r="O318" t="str">
+        <v/>
+      </c>
+      <c r="P318" t="str">
+        <v/>
+      </c>
+      <c r="Q318" t="str">
+        <v/>
+      </c>
+      <c r="R318" t="str">
+        <v>Freelance;Replacement</v>
+      </c>
+      <c r="S318" t="str">
+        <v>Replace Ridho</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>nNl-hAIbd0m07BT7kGN8TsgABkXI</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Account Executive KCM</v>
+      </c>
+      <c r="C319" t="str">
+        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+      </c>
+      <c r="D319" t="str">
+        <v/>
+      </c>
+      <c r="E319" t="str">
+        <v>Not started</v>
+      </c>
+      <c r="F319" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G319" t="str">
+        <v/>
+      </c>
+      <c r="H319" t="str">
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
+      </c>
+      <c r="I319" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="J319" t="str">
+        <v/>
+      </c>
+      <c r="K319" t="str">
+        <v/>
+      </c>
+      <c r="L319" t="str">
+        <v/>
+      </c>
+      <c r="M319" t="str">
+        <v>false</v>
+      </c>
+      <c r="N319" t="str">
+        <v/>
+      </c>
+      <c r="O319" t="str">
+        <v/>
+      </c>
+      <c r="P319" t="str">
+        <v/>
+      </c>
+      <c r="Q319" t="str">
+        <v/>
+      </c>
+      <c r="R319" t="str">
+        <v/>
+      </c>
+      <c r="S319" t="str">
+        <v>Replace Bangkit yang digeser ke tim mas tomi</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>4ErHzmlDxUeTwJhUWrFdjsgABfo2</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Account Executive KCM</v>
+      </c>
+      <c r="C320" t="str">
+        <v>QYOtSHwRQ0ufNLTfEIceRMgAJp6S</v>
+      </c>
+      <c r="D320" t="str">
+        <v/>
+      </c>
+      <c r="E320" t="str">
+        <v>Not started</v>
+      </c>
+      <c r="F320" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G320" t="str">
+        <v/>
+      </c>
+      <c r="H320" t="str">
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
+      </c>
+      <c r="I320" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="J320" t="str">
+        <v/>
+      </c>
+      <c r="K320" t="str">
+        <v/>
+      </c>
+      <c r="L320" t="str">
+        <v/>
+      </c>
+      <c r="M320" t="str">
+        <v>false</v>
+      </c>
+      <c r="N320" t="str">
+        <v/>
+      </c>
+      <c r="O320" t="str">
+        <v/>
+      </c>
+      <c r="P320" t="str">
+        <v/>
+      </c>
+      <c r="Q320" t="str">
+        <v/>
+      </c>
+      <c r="R320" t="str">
+        <v/>
+      </c>
+      <c r="S320" t="str">
+        <v>Replace Gito pindah ke tim Mba Tita</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>bzb3uAzmq0yifTDVYXs5SMgADLCT</v>
+      </c>
+      <c r="B321" t="str">
+        <v>MUA Intern</v>
+      </c>
+      <c r="C321" t="str">
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+      </c>
+      <c r="D321" t="str">
+        <v/>
+      </c>
+      <c r="E321" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F321" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G321" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="H321" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I321" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="J321" t="str">
+        <v/>
+      </c>
+      <c r="K321" t="str">
+        <v/>
+      </c>
+      <c r="L321" t="str">
+        <v/>
+      </c>
+      <c r="M321" t="str">
+        <v>false</v>
+      </c>
+      <c r="N321" t="str">
+        <v/>
+      </c>
+      <c r="O321" t="str">
+        <v/>
+      </c>
+      <c r="P321" t="str">
+        <v/>
+      </c>
+      <c r="Q321" t="str">
+        <v/>
+      </c>
+      <c r="R321" t="str">
+        <v>Intern-Paid</v>
+      </c>
+      <c r="S321" t="str">
+        <v>Melanjutkan intern a/n Syifa dari Maganghub Kemnaker Batch 2</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>YXJn_d_IPE6nQ3WawHh_r8gABqZK</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Intern Employer Branding KG Media</v>
+      </c>
+      <c r="C322" t="str">
+        <v>kuJ6IafvyUC7jpAlgn80lcgAFPG2</v>
+      </c>
+      <c r="D322" t="str">
+        <v/>
+      </c>
+      <c r="E322" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F322" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G322" t="str">
+        <v/>
+      </c>
+      <c r="H322" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I322" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="J322" t="str">
+        <v/>
+      </c>
+      <c r="K322" t="str">
+        <v/>
+      </c>
+      <c r="L322" t="str">
+        <v/>
+      </c>
+      <c r="M322" t="str">
+        <v>false</v>
+      </c>
+      <c r="N322" t="str">
+        <v/>
+      </c>
+      <c r="O322" t="str">
+        <v/>
+      </c>
+      <c r="P322" t="str">
+        <v/>
+      </c>
+      <c r="Q322" t="str">
+        <v/>
+      </c>
+      <c r="R322" t="str">
+        <v>Unpaid</v>
+      </c>
+      <c r="S322" t="str">
+        <v>buat di tim Lestari KG Media (additional)</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>I8e0xK_4WU66_3ycDNM8NcgAHn2h</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Digital Archivist Intern</v>
+      </c>
+      <c r="C323" t="str">
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+      </c>
+      <c r="D323" t="str">
+        <v/>
+      </c>
+      <c r="E323" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F323" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G323" t="str">
+        <v/>
+      </c>
+      <c r="H323" t="str">
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
+      </c>
+      <c r="I323" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="J323" t="str">
+        <v/>
+      </c>
+      <c r="K323" t="str">
+        <v/>
+      </c>
+      <c r="L323" t="str">
+        <v/>
+      </c>
+      <c r="M323" t="str">
+        <v>false</v>
+      </c>
+      <c r="N323" t="str">
+        <v/>
+      </c>
+      <c r="O323" t="str">
+        <v/>
+      </c>
+      <c r="P323" t="str">
+        <v/>
+      </c>
+      <c r="Q323" t="str">
+        <v/>
+      </c>
+      <c r="R323" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>cPz89enrUEKB0B4vnLoMEMgAL3j9</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Account Executive Pasangiklan</v>
+      </c>
+      <c r="C324" t="str">
+        <v>2e5rTnOsO0GZly5qiC086MgABQDs</v>
+      </c>
+      <c r="D324" t="str">
+        <v/>
+      </c>
+      <c r="E324" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F324" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G324" t="str">
+        <v>00672709-9ae7-4622-852f-f212507435f4</v>
+      </c>
+      <c r="H324" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I324" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="J324" t="str">
+        <v/>
+      </c>
+      <c r="K324" t="str">
+        <v/>
+      </c>
+      <c r="L324" t="str">
+        <v/>
+      </c>
+      <c r="M324" t="str">
+        <v>false</v>
+      </c>
+      <c r="N324" t="str">
+        <v/>
+      </c>
+      <c r="O324" t="str">
+        <v/>
+      </c>
+      <c r="P324" t="str">
+        <v/>
+      </c>
+      <c r="Q324" t="str">
+        <v/>
+      </c>
+      <c r="R324" t="str">
+        <v>KKWT</v>
+      </c>
+      <c r="S324" t="str">
+        <v>Replace Moza</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>LKpiEsrzb0CetoK8u550KsgAONAA</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Host &amp; Creative</v>
+      </c>
+      <c r="C325" t="str">
+        <v>CVRgI9rK9EKlvUayGaR28cgACw4O</v>
+      </c>
+      <c r="D325" t="str">
+        <v/>
+      </c>
+      <c r="E325" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="F325" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G325" t="str">
+        <v/>
+      </c>
+      <c r="H325" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I325" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="J325" t="str">
+        <v/>
+      </c>
+      <c r="K325" t="str">
+        <v/>
+      </c>
+      <c r="L325" t="str">
+        <v/>
+      </c>
+      <c r="M325" t="str">
+        <v>false</v>
+      </c>
+      <c r="N325" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="O325" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="P325" t="str">
+        <v/>
+      </c>
+      <c r="Q325" t="str">
+        <v/>
+      </c>
+      <c r="R325" t="str">
+        <v/>
+      </c>
+      <c r="S325" t="str">
+        <v>Additional - alih status Rega dari freelance ke KKWT</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>a6kDTvMIX0eZhPGvFZSETMgAJ_DU</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Host &amp; Creative</v>
+      </c>
+      <c r="C326" t="str">
+        <v>wZXGQRPtEUCxklaro6abScgAM159</v>
+      </c>
+      <c r="D326" t="str">
+        <v/>
+      </c>
+      <c r="E326" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="F326" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+      </c>
+      <c r="I326" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="J326" t="str">
+        <v/>
+      </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
+      <c r="L326" t="str">
+        <v/>
+      </c>
+      <c r="M326" t="str">
+        <v>false</v>
+      </c>
+      <c r="N326" t="str">
+        <v/>
+      </c>
+      <c r="O326" t="str">
+        <v/>
+      </c>
+      <c r="P326" t="str">
+        <v/>
+      </c>
+      <c r="Q326" t="str">
+        <v/>
+      </c>
+      <c r="R326" t="str">
+        <v/>
+      </c>
+      <c r="S326" t="str">
+        <v>Replace Jessica Emmanuela -&gt; pindah sales government</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S314"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S326"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -38110,7 +39526,7 @@
         <v>tmoBkXOwC0-VxbVJW4TOHsgAJ7KY</v>
       </c>
       <c r="B9" t="str">
-        <v>In Progress (Untuk Task selain Recruitment Reguler)</v>
+        <v>Untuk Task selain Recruitment Reguler</v>
       </c>
     </row>
     <row r="10">
@@ -38130,7 +39546,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -38150,40 +39566,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>acc533b1-a4ba-4dd5-b21d-cd5a1cc52392</v>
+        <v>bea4b736-604e-4c3c-9844-ec5583740132</v>
       </c>
       <c r="B2" t="str">
-        <v>Adelia Galuh H</v>
+        <v>Netri Alia Rahmi</v>
       </c>
       <c r="C2" t="str">
-        <v>adelia.galuh@kompas.com</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ff348c23-4ec9-4469-a90c-2fe5d3a105c8</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Novinda Riski</v>
-      </c>
-      <c r="C3" t="str">
-        <v>novinda.riski@kompas.com</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>00672709-9ae7-4622-852f-f212507435f4</v>
-      </c>
-      <c r="B4" t="str">
-        <v>HR Development</v>
-      </c>
-      <c r="C4" t="str">
-        <v>hr.development@kompas.com</v>
+        <v>netri.alia@kompas.com</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>